--- a/115年7月預劃匯入版 (1).xlsx
+++ b/115年7月預劃匯入版 (1).xlsx
@@ -1,17 +1,25 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\T02363\Downloads\ShiftScheduler\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <bookViews>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="10935"/>
+  </bookViews>
   <sheets>
-    <sheet state="visible" name="工作表1" sheetId="1" r:id="rId5"/>
+    <sheet name="工作表1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr/>
+  <calcPr calcId="162913"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="60">
   <si>
     <t>員編
 ID No.</t>
@@ -129,17 +137,21 @@
   <si>
     <r>
       <rPr>
+        <sz val="24"/>
+        <color theme="1"/>
         <rFont val="細明體-ExtB"/>
-        <color theme="1"/>
-        <sz val="24.0"/>
+        <family val="1"/>
+        <charset val="136"/>
       </rPr>
       <t>𡍼</t>
     </r>
     <r>
       <rPr>
+        <sz val="24"/>
+        <color theme="1"/>
         <rFont val="微軟正黑體"/>
-        <color theme="1"/>
-        <sz val="24.0"/>
+        <family val="2"/>
+        <charset val="136"/>
       </rPr>
       <t>文妤</t>
     </r>
@@ -163,56 +175,158 @@
     <t>r</t>
   </si>
   <si>
-    <t>T02612</t>
-  </si>
-  <si>
-    <t>蕭曉琦</t>
-  </si>
-  <si>
     <t>T02613</t>
   </si>
   <si>
     <t>張雅荃</t>
+  </si>
+  <si>
+    <t>T02758</t>
+  </si>
+  <si>
+    <t>王映心</t>
+  </si>
+  <si>
+    <t>T02762</t>
+  </si>
+  <si>
+    <t>周怡萍</t>
+  </si>
+  <si>
+    <t>T02763</t>
+  </si>
+  <si>
+    <t>陳佑融</t>
+  </si>
+  <si>
+    <t>T02769</t>
+  </si>
+  <si>
+    <t>吳東翰</t>
+  </si>
+  <si>
+    <t>T02776</t>
+  </si>
+  <si>
+    <t>陳怡臻</t>
+  </si>
+  <si>
+    <t>T02777</t>
+  </si>
+  <si>
+    <t>彭裕涵</t>
+  </si>
+  <si>
+    <t>R</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>r</t>
+    <phoneticPr fontId="11" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="d"/>
-    <numFmt numFmtId="165" formatCode="[DBNum1][$-404]General"/>
+    <numFmt numFmtId="176" formatCode="d"/>
+    <numFmt numFmtId="177" formatCode="[DBNum1][$-404]General"/>
   </numFmts>
-  <fonts count="5">
+  <fonts count="13">
     <font>
-      <sz val="12.0"/>
+      <sz val="12"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="24.0"/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="136"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="24"/>
       <color rgb="FFFF0000"/>
       <name val="Microsoft JhengHei"/>
+      <family val="2"/>
+      <charset val="136"/>
     </font>
     <font>
-      <sz val="24.0"/>
+      <sz val="24"/>
       <color theme="1"/>
       <name val="Microsoft JhengHei"/>
+      <family val="2"/>
+      <charset val="136"/>
     </font>
-    <font/>
     <font>
-      <sz val="24.0"/>
+      <sz val="12"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="24"/>
       <color rgb="FF00B050"/>
       <name val="Microsoft JhengHei"/>
+      <family val="2"/>
+      <charset val="136"/>
+    </font>
+    <font>
+      <sz val="24"/>
+      <color theme="1"/>
+      <name val="細明體-ExtB"/>
+      <family val="1"/>
+      <charset val="136"/>
+    </font>
+    <font>
+      <sz val="24"/>
+      <color theme="1"/>
+      <name val="微軟正黑體"/>
+      <family val="2"/>
+      <charset val="136"/>
+    </font>
+    <font>
+      <sz val="24"/>
+      <name val="微軟正黑體"/>
+      <family val="2"/>
+      <charset val="136"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="Calibri"/>
+      <family val="3"/>
+      <charset val="136"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="新細明體"/>
+      <family val="1"/>
+      <charset val="136"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="新細明體"/>
+      <family val="1"/>
+      <charset val="136"/>
+    </font>
+    <font>
+      <sz val="24"/>
+      <color rgb="FFFF0000"/>
+      <name val="微軟正黑體"/>
+      <family val="2"/>
+      <charset val="136"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="lightGray"/>
+      <patternFill patternType="gray125"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -226,16 +340,31 @@
         <bgColor rgb="FFE5E5E5"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.249977111117893"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="33">
-    <border/>
+  <borders count="44">
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
     <border>
       <left style="medium">
         <color rgb="FF000000"/>
       </left>
+      <right/>
       <top style="medium">
         <color rgb="FF000000"/>
       </top>
+      <bottom/>
+      <diagonal/>
     </border>
     <border>
       <left style="medium">
@@ -247,6 +376,8 @@
       <top style="medium">
         <color rgb="FF000000"/>
       </top>
+      <bottom/>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -258,6 +389,8 @@
       <top style="medium">
         <color rgb="FF000000"/>
       </top>
+      <bottom/>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -272,252 +405,21 @@
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left style="medium">
         <color rgb="FF000000"/>
       </left>
+      <right/>
+      <top/>
       <bottom style="medium">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left style="medium">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="medium">
-        <color rgb="FF000000"/>
-      </right>
-    </border>
-    <border>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="medium">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="medium">
-        <color rgb="FF000000"/>
-      </top>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="medium">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="medium">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="medium">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-    </border>
-    <border>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="medium">
-        <color rgb="FF000000"/>
-      </right>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="medium">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="medium">
-        <color rgb="FF000000"/>
-      </right>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF000000"/>
-      </bottom>
-    </border>
-    <border>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF000000"/>
-      </bottom>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="double">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="medium">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="double">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="double">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-    </border>
-    <border>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="double">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-    </border>
-    <border>
-      <left style="thin">
         <color rgb="FF000000"/>
       </left>
       <right style="thin">
@@ -525,22 +427,75 @@
       </right>
       <top/>
       <bottom/>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
         <color rgb="FF000000"/>
       </left>
       <right style="thin">
         <color rgb="FF000000"/>
       </right>
-    </border>
-    <border>
-      <right style="thin">
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="medium">
         <color rgb="FF000000"/>
       </right>
-    </border>
-    <border>
-      <left style="medium">
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
         <color rgb="FF000000"/>
       </left>
       <right style="thin">
@@ -549,23 +504,219 @@
       <top style="thin">
         <color rgb="FF000000"/>
       </top>
-      <bottom style="medium">
+      <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
         <color rgb="FF000000"/>
       </left>
       <right style="medium">
         <color rgb="FF000000"/>
       </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="double">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="double">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="double">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="double">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
       <top style="thin">
         <color rgb="FF000000"/>
       </top>
       <bottom style="medium">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -580,8 +731,10 @@
       <bottom style="medium">
         <color rgb="FF000000"/>
       </bottom>
-    </border>
-    <border>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
       <right style="thin">
         <color rgb="FF000000"/>
       </right>
@@ -591,160 +744,496 @@
       <bottom style="medium">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
+  <cellStyleXfs count="4">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="46">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="1" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="2" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="3" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="4" fillId="2" fontId="2" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="5" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+  <cellXfs count="69">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf borderId="6" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="3" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="3" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf borderId="7" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="8" fillId="0" fontId="2" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="165" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf borderId="9" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf borderId="10" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf borderId="11" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf borderId="12" fillId="3" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf borderId="12" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf borderId="13" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf borderId="14" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf borderId="15" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf borderId="16" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf borderId="17" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf borderId="12" fillId="3" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf borderId="18" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf borderId="19" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf borderId="20" fillId="3" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf borderId="20" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf borderId="21" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf borderId="22" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf borderId="23" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf borderId="24" fillId="3" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf borderId="24" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf borderId="25" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf borderId="12" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" vertical="center"/>
-    </xf>
-    <xf borderId="12" fillId="3" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf borderId="12" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf borderId="6" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf borderId="7" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf borderId="26" fillId="3" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" vertical="center"/>
-    </xf>
-    <xf borderId="27" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf borderId="28" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf borderId="26" fillId="3" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf borderId="29" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf borderId="30" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf borderId="31" fillId="3" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf borderId="31" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf borderId="32" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="30" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="31" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="32" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="33" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="34" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="35" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="36" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="37" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="30" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="38" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="39" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="38" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="31" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="39" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="36" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="40" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="41" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="40" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="37" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="40" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="40" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="41" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="34" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="42" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="42" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="35" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="43" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="38" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="38" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="1">
-    <cellStyle xfId="0" name="Normal" builtinId="0"/>
+  <cellStyles count="4">
+    <cellStyle name="一般" xfId="0" builtinId="0"/>
+    <cellStyle name="一般 9" xfId="1"/>
+    <cellStyle name="一般_201009draft" xfId="3"/>
+    <cellStyle name="一般_AB班表早晚班交錯POR_2007-roster_2007-roster" xfId="2"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="12">
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+  </dxfs>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
 </file>
 
 <file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
@@ -752,7 +1241,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Sheets">
   <a:themeElements>
     <a:clrScheme name="Sheets">
       <a:dk1>
@@ -942,1129 +1431,1335 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-  <sheetPr>
-    <pageSetUpPr/>
-  </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="11.22" defaultRowHeight="15.0"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:AE999"/>
+  <sheetFormatPr defaultColWidth="11.25" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="5.33"/>
-    <col customWidth="1" min="2" max="2" width="12.11"/>
-    <col customWidth="1" min="3" max="3" width="16.67"/>
-    <col customWidth="1" min="4" max="31" width="16.78"/>
+    <col min="1" max="1" width="5.375" customWidth="1"/>
+    <col min="2" max="2" width="12.125" customWidth="1"/>
+    <col min="3" max="3" width="16.625" customWidth="1"/>
+    <col min="4" max="31" width="16.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="30.75" customHeight="1">
-      <c r="A1" s="1"/>
-      <c r="B1" s="2" t="s">
+    <row r="1" spans="1:31" ht="30.75" customHeight="1">
+      <c r="A1" s="34"/>
+      <c r="B1" s="36" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="4">
-        <v>46208.0</v>
-      </c>
-      <c r="E1" s="4">
-        <v>46209.0</v>
-      </c>
-      <c r="F1" s="4">
-        <v>46210.0</v>
-      </c>
-      <c r="G1" s="4">
-        <v>46211.0</v>
-      </c>
-      <c r="H1" s="4">
-        <v>46212.0</v>
-      </c>
-      <c r="I1" s="4">
-        <v>46213.0</v>
-      </c>
-      <c r="J1" s="4">
-        <v>46214.0</v>
-      </c>
-      <c r="K1" s="4">
-        <v>46215.0</v>
-      </c>
-      <c r="L1" s="4">
-        <v>46216.0</v>
-      </c>
-      <c r="M1" s="4">
-        <v>46217.0</v>
-      </c>
-      <c r="N1" s="4">
-        <v>46218.0</v>
-      </c>
-      <c r="O1" s="4">
-        <v>46219.0</v>
-      </c>
-      <c r="P1" s="4">
-        <v>46220.0</v>
-      </c>
-      <c r="Q1" s="4">
-        <v>46221.0</v>
-      </c>
-      <c r="R1" s="4">
-        <v>46222.0</v>
-      </c>
-      <c r="S1" s="4">
-        <v>46223.0</v>
-      </c>
-      <c r="T1" s="4">
-        <v>46224.0</v>
-      </c>
-      <c r="U1" s="4">
-        <v>46225.0</v>
-      </c>
-      <c r="V1" s="4">
-        <v>46226.0</v>
-      </c>
-      <c r="W1" s="4">
-        <v>46227.0</v>
-      </c>
-      <c r="X1" s="4">
-        <v>46228.0</v>
-      </c>
-      <c r="Y1" s="4">
-        <v>46229.0</v>
-      </c>
-      <c r="Z1" s="4">
-        <v>46230.0</v>
-      </c>
-      <c r="AA1" s="4">
-        <v>46231.0</v>
-      </c>
-      <c r="AB1" s="4">
-        <v>46232.0</v>
-      </c>
-      <c r="AC1" s="4">
-        <v>46233.0</v>
-      </c>
-      <c r="AD1" s="4">
-        <v>46234.0</v>
-      </c>
-      <c r="AE1" s="4">
-        <v>46235.0</v>
+      <c r="D1" s="2">
+        <v>46208</v>
+      </c>
+      <c r="E1" s="2">
+        <v>46209</v>
+      </c>
+      <c r="F1" s="2">
+        <v>46210</v>
+      </c>
+      <c r="G1" s="2">
+        <v>46211</v>
+      </c>
+      <c r="H1" s="2">
+        <v>46212</v>
+      </c>
+      <c r="I1" s="2">
+        <v>46213</v>
+      </c>
+      <c r="J1" s="2">
+        <v>46214</v>
+      </c>
+      <c r="K1" s="2">
+        <v>46215</v>
+      </c>
+      <c r="L1" s="2">
+        <v>46216</v>
+      </c>
+      <c r="M1" s="2">
+        <v>46217</v>
+      </c>
+      <c r="N1" s="2">
+        <v>46218</v>
+      </c>
+      <c r="O1" s="2">
+        <v>46219</v>
+      </c>
+      <c r="P1" s="2">
+        <v>46220</v>
+      </c>
+      <c r="Q1" s="2">
+        <v>46221</v>
+      </c>
+      <c r="R1" s="2">
+        <v>46222</v>
+      </c>
+      <c r="S1" s="2">
+        <v>46223</v>
+      </c>
+      <c r="T1" s="2">
+        <v>46224</v>
+      </c>
+      <c r="U1" s="2">
+        <v>46225</v>
+      </c>
+      <c r="V1" s="2">
+        <v>46226</v>
+      </c>
+      <c r="W1" s="2">
+        <v>46227</v>
+      </c>
+      <c r="X1" s="2">
+        <v>46228</v>
+      </c>
+      <c r="Y1" s="2">
+        <v>46229</v>
+      </c>
+      <c r="Z1" s="2">
+        <v>46230</v>
+      </c>
+      <c r="AA1" s="2">
+        <v>46231</v>
+      </c>
+      <c r="AB1" s="2">
+        <v>46232</v>
+      </c>
+      <c r="AC1" s="2">
+        <v>46233</v>
+      </c>
+      <c r="AD1" s="2">
+        <v>46234</v>
+      </c>
+      <c r="AE1" s="2">
+        <v>46235</v>
       </c>
     </row>
-    <row r="2" ht="15.75" customHeight="1">
-      <c r="A2" s="5"/>
-      <c r="B2" s="6"/>
-      <c r="C2" s="7" t="s">
+    <row r="2" spans="1:31" ht="15.75" customHeight="1">
+      <c r="A2" s="35"/>
+      <c r="B2" s="37"/>
+      <c r="C2" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="8" t="str">
-        <f t="shared" ref="D2:AD2" si="1">RIGHT(TEXT(D1,"[$-404]aaaa;@"),1)</f>
-        <v>a</v>
-      </c>
-      <c r="E2" s="8" t="str">
-        <f t="shared" si="1"/>
-        <v>a</v>
-      </c>
-      <c r="F2" s="8" t="str">
-        <f t="shared" si="1"/>
-        <v>a</v>
-      </c>
-      <c r="G2" s="8" t="str">
-        <f t="shared" si="1"/>
-        <v>a</v>
-      </c>
-      <c r="H2" s="8" t="str">
-        <f t="shared" si="1"/>
-        <v>a</v>
-      </c>
-      <c r="I2" s="8" t="str">
-        <f t="shared" si="1"/>
-        <v>a</v>
-      </c>
-      <c r="J2" s="8" t="str">
-        <f t="shared" si="1"/>
-        <v>a</v>
-      </c>
-      <c r="K2" s="8" t="str">
-        <f t="shared" si="1"/>
-        <v>a</v>
-      </c>
-      <c r="L2" s="8" t="str">
-        <f t="shared" si="1"/>
-        <v>a</v>
-      </c>
-      <c r="M2" s="8" t="str">
-        <f t="shared" si="1"/>
-        <v>a</v>
-      </c>
-      <c r="N2" s="8" t="str">
-        <f t="shared" si="1"/>
-        <v>a</v>
-      </c>
-      <c r="O2" s="8" t="str">
-        <f t="shared" si="1"/>
-        <v>a</v>
-      </c>
-      <c r="P2" s="8" t="str">
-        <f t="shared" si="1"/>
-        <v>a</v>
-      </c>
-      <c r="Q2" s="8" t="str">
-        <f t="shared" si="1"/>
-        <v>a</v>
-      </c>
-      <c r="R2" s="8" t="str">
-        <f t="shared" si="1"/>
-        <v>a</v>
-      </c>
-      <c r="S2" s="8" t="str">
-        <f t="shared" si="1"/>
-        <v>a</v>
-      </c>
-      <c r="T2" s="8" t="str">
-        <f t="shared" si="1"/>
-        <v>a</v>
-      </c>
-      <c r="U2" s="8" t="str">
-        <f t="shared" si="1"/>
-        <v>a</v>
-      </c>
-      <c r="V2" s="8" t="str">
-        <f t="shared" si="1"/>
-        <v>a</v>
-      </c>
-      <c r="W2" s="8" t="str">
-        <f t="shared" si="1"/>
-        <v>a</v>
-      </c>
-      <c r="X2" s="8" t="str">
-        <f t="shared" si="1"/>
-        <v>a</v>
-      </c>
-      <c r="Y2" s="8" t="str">
-        <f t="shared" si="1"/>
-        <v>a</v>
-      </c>
-      <c r="Z2" s="8" t="str">
-        <f t="shared" si="1"/>
-        <v>a</v>
-      </c>
-      <c r="AA2" s="8" t="str">
-        <f t="shared" si="1"/>
-        <v>a</v>
-      </c>
-      <c r="AB2" s="8" t="str">
-        <f t="shared" si="1"/>
-        <v>a</v>
-      </c>
-      <c r="AC2" s="8" t="str">
-        <f t="shared" si="1"/>
-        <v>a</v>
-      </c>
-      <c r="AD2" s="8" t="str">
-        <f t="shared" si="1"/>
-        <v>a</v>
-      </c>
-      <c r="AE2" s="9"/>
+      <c r="D2" s="4" t="str">
+        <f t="shared" ref="D2:AD2" si="0">RIGHT(TEXT(D1,"[$-404]aaaa;@"),1)</f>
+        <v>日</v>
+      </c>
+      <c r="E2" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>一</v>
+      </c>
+      <c r="F2" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>二</v>
+      </c>
+      <c r="G2" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>三</v>
+      </c>
+      <c r="H2" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>四</v>
+      </c>
+      <c r="I2" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>五</v>
+      </c>
+      <c r="J2" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>六</v>
+      </c>
+      <c r="K2" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>日</v>
+      </c>
+      <c r="L2" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>一</v>
+      </c>
+      <c r="M2" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>二</v>
+      </c>
+      <c r="N2" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>三</v>
+      </c>
+      <c r="O2" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>四</v>
+      </c>
+      <c r="P2" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>五</v>
+      </c>
+      <c r="Q2" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>六</v>
+      </c>
+      <c r="R2" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>日</v>
+      </c>
+      <c r="S2" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>一</v>
+      </c>
+      <c r="T2" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>二</v>
+      </c>
+      <c r="U2" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>三</v>
+      </c>
+      <c r="V2" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>四</v>
+      </c>
+      <c r="W2" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>五</v>
+      </c>
+      <c r="X2" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>六</v>
+      </c>
+      <c r="Y2" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>日</v>
+      </c>
+      <c r="Z2" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>一</v>
+      </c>
+      <c r="AA2" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>二</v>
+      </c>
+      <c r="AB2" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>三</v>
+      </c>
+      <c r="AC2" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>四</v>
+      </c>
+      <c r="AD2" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>五</v>
+      </c>
+      <c r="AE2" s="5"/>
     </row>
-    <row r="3" ht="15.75" customHeight="1">
-      <c r="A3" s="10" t="s">
+    <row r="3" spans="1:31" ht="15.75" customHeight="1">
+      <c r="A3" s="38" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="11" t="s">
+      <c r="B3" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="C3" s="12" t="s">
+      <c r="C3" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="D3" s="13"/>
-      <c r="E3" s="14"/>
-      <c r="F3" s="14"/>
-      <c r="G3" s="14"/>
-      <c r="H3" s="14"/>
-      <c r="I3" s="15"/>
-      <c r="J3" s="13"/>
-      <c r="K3" s="13"/>
-      <c r="L3" s="14"/>
-      <c r="M3" s="14"/>
-      <c r="N3" s="14" t="s">
+      <c r="D3" s="8"/>
+      <c r="E3" s="9"/>
+      <c r="F3" s="9"/>
+      <c r="G3" s="9"/>
+      <c r="H3" s="9"/>
+      <c r="I3" s="10"/>
+      <c r="J3" s="8"/>
+      <c r="K3" s="8"/>
+      <c r="L3" s="9"/>
+      <c r="M3" s="9"/>
+      <c r="N3" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="O3" s="16" t="s">
+      <c r="O3" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="P3" s="15"/>
-      <c r="Q3" s="13"/>
-      <c r="R3" s="13"/>
-      <c r="S3" s="14"/>
-      <c r="T3" s="14"/>
-      <c r="U3" s="14"/>
-      <c r="V3" s="14"/>
-      <c r="W3" s="15"/>
-      <c r="X3" s="13" t="s">
+      <c r="P3" s="10"/>
+      <c r="Q3" s="8"/>
+      <c r="R3" s="8"/>
+      <c r="S3" s="9"/>
+      <c r="T3" s="9"/>
+      <c r="U3" s="9"/>
+      <c r="V3" s="9"/>
+      <c r="W3" s="10"/>
+      <c r="X3" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="Y3" s="13" t="s">
+      <c r="Y3" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="Z3" s="14"/>
-      <c r="AA3" s="14"/>
-      <c r="AB3" s="14"/>
-      <c r="AC3" s="14"/>
-      <c r="AD3" s="14"/>
-      <c r="AE3" s="17"/>
+      <c r="Z3" s="9"/>
+      <c r="AA3" s="9"/>
+      <c r="AB3" s="9"/>
+      <c r="AC3" s="9"/>
+      <c r="AD3" s="9"/>
+      <c r="AE3" s="12"/>
     </row>
-    <row r="4" ht="15.75" customHeight="1">
-      <c r="A4" s="18"/>
-      <c r="B4" s="19" t="s">
+    <row r="4" spans="1:31" ht="15.75" customHeight="1">
+      <c r="A4" s="39"/>
+      <c r="B4" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="C4" s="20" t="s">
+      <c r="C4" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="D4" s="13"/>
-      <c r="E4" s="14"/>
-      <c r="F4" s="14"/>
-      <c r="G4" s="14"/>
-      <c r="H4" s="14"/>
-      <c r="I4" s="15"/>
-      <c r="J4" s="13"/>
-      <c r="K4" s="13"/>
-      <c r="L4" s="14"/>
-      <c r="M4" s="14"/>
-      <c r="N4" s="14"/>
-      <c r="O4" s="14"/>
-      <c r="P4" s="15"/>
-      <c r="Q4" s="13"/>
-      <c r="R4" s="13"/>
-      <c r="S4" s="14"/>
-      <c r="T4" s="14"/>
-      <c r="U4" s="14"/>
-      <c r="V4" s="14"/>
-      <c r="W4" s="15"/>
-      <c r="X4" s="13"/>
-      <c r="Y4" s="13"/>
-      <c r="Z4" s="14" t="s">
+      <c r="D4" s="8"/>
+      <c r="E4" s="9"/>
+      <c r="F4" s="9"/>
+      <c r="G4" s="9"/>
+      <c r="H4" s="9"/>
+      <c r="I4" s="10"/>
+      <c r="J4" s="8"/>
+      <c r="K4" s="8"/>
+      <c r="L4" s="9"/>
+      <c r="M4" s="9"/>
+      <c r="N4" s="9"/>
+      <c r="O4" s="9"/>
+      <c r="P4" s="10"/>
+      <c r="Q4" s="8"/>
+      <c r="R4" s="8"/>
+      <c r="S4" s="9"/>
+      <c r="T4" s="9"/>
+      <c r="U4" s="9"/>
+      <c r="V4" s="9"/>
+      <c r="W4" s="10"/>
+      <c r="X4" s="8"/>
+      <c r="Y4" s="8"/>
+      <c r="Z4" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="AA4" s="14" t="s">
+      <c r="AA4" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="AB4" s="14" t="s">
+      <c r="AB4" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="AC4" s="14" t="s">
+      <c r="AC4" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="AD4" s="14"/>
-      <c r="AE4" s="17"/>
+      <c r="AD4" s="9"/>
+      <c r="AE4" s="12"/>
     </row>
-    <row r="5" ht="15.75" customHeight="1">
-      <c r="A5" s="18"/>
-      <c r="B5" s="19" t="s">
+    <row r="5" spans="1:31" ht="15.75" customHeight="1">
+      <c r="A5" s="39"/>
+      <c r="B5" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="C5" s="20" t="s">
+      <c r="C5" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="D5" s="13"/>
-      <c r="E5" s="14"/>
-      <c r="F5" s="14"/>
-      <c r="G5" s="14"/>
-      <c r="H5" s="14"/>
-      <c r="I5" s="15"/>
-      <c r="J5" s="13"/>
-      <c r="K5" s="13"/>
-      <c r="L5" s="14"/>
-      <c r="M5" s="14"/>
-      <c r="N5" s="14" t="s">
+      <c r="D5" s="8"/>
+      <c r="E5" s="9"/>
+      <c r="F5" s="9"/>
+      <c r="G5" s="9"/>
+      <c r="H5" s="9"/>
+      <c r="I5" s="10"/>
+      <c r="J5" s="8"/>
+      <c r="K5" s="8"/>
+      <c r="L5" s="9"/>
+      <c r="M5" s="9"/>
+      <c r="N5" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="O5" s="14" t="s">
+      <c r="O5" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="P5" s="15"/>
-      <c r="Q5" s="13"/>
-      <c r="R5" s="13"/>
-      <c r="S5" s="14"/>
-      <c r="T5" s="14"/>
-      <c r="U5" s="14"/>
-      <c r="V5" s="14"/>
-      <c r="W5" s="15"/>
-      <c r="X5" s="13" t="s">
+      <c r="P5" s="10"/>
+      <c r="Q5" s="8"/>
+      <c r="R5" s="8"/>
+      <c r="S5" s="9"/>
+      <c r="T5" s="9"/>
+      <c r="U5" s="9"/>
+      <c r="V5" s="9"/>
+      <c r="W5" s="10"/>
+      <c r="X5" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="Y5" s="13" t="s">
+      <c r="Y5" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="Z5" s="14"/>
-      <c r="AA5" s="14"/>
-      <c r="AB5" s="14"/>
-      <c r="AC5" s="14"/>
-      <c r="AD5" s="14"/>
-      <c r="AE5" s="17"/>
+      <c r="Z5" s="9"/>
+      <c r="AA5" s="9"/>
+      <c r="AB5" s="9"/>
+      <c r="AC5" s="9"/>
+      <c r="AD5" s="9"/>
+      <c r="AE5" s="12"/>
     </row>
-    <row r="6" ht="15.75" customHeight="1">
-      <c r="A6" s="18"/>
-      <c r="B6" s="19" t="s">
+    <row r="6" spans="1:31" ht="15.75" customHeight="1">
+      <c r="A6" s="39"/>
+      <c r="B6" s="13" t="s">
         <v>13</v>
       </c>
-      <c r="C6" s="20" t="s">
+      <c r="C6" s="14" t="s">
         <v>14</v>
       </c>
-      <c r="D6" s="21" t="s">
+      <c r="D6" s="15" t="s">
         <v>10</v>
       </c>
-      <c r="E6" s="21" t="s">
+      <c r="E6" s="15" t="s">
         <v>7</v>
       </c>
-      <c r="F6" s="14" t="s">
+      <c r="F6" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="G6" s="14" t="s">
+      <c r="G6" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="H6" s="14" t="s">
+      <c r="H6" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="I6" s="15"/>
-      <c r="J6" s="13"/>
-      <c r="K6" s="13"/>
-      <c r="L6" s="14"/>
-      <c r="M6" s="14"/>
-      <c r="N6" s="14"/>
-      <c r="O6" s="14"/>
-      <c r="P6" s="14"/>
-      <c r="Q6" s="13"/>
-      <c r="R6" s="13"/>
-      <c r="S6" s="14"/>
-      <c r="T6" s="14"/>
-      <c r="U6" s="14"/>
-      <c r="V6" s="14"/>
-      <c r="W6" s="15"/>
-      <c r="X6" s="13"/>
-      <c r="Y6" s="13"/>
-      <c r="Z6" s="14"/>
-      <c r="AA6" s="14"/>
-      <c r="AB6" s="14"/>
-      <c r="AC6" s="14"/>
-      <c r="AD6" s="14"/>
-      <c r="AE6" s="17"/>
+      <c r="I6" s="10"/>
+      <c r="J6" s="8"/>
+      <c r="K6" s="8"/>
+      <c r="L6" s="9"/>
+      <c r="M6" s="9"/>
+      <c r="N6" s="9"/>
+      <c r="O6" s="9"/>
+      <c r="P6" s="9"/>
+      <c r="Q6" s="8"/>
+      <c r="R6" s="8"/>
+      <c r="S6" s="9"/>
+      <c r="T6" s="9"/>
+      <c r="U6" s="9"/>
+      <c r="V6" s="9"/>
+      <c r="W6" s="10"/>
+      <c r="X6" s="8"/>
+      <c r="Y6" s="8"/>
+      <c r="Z6" s="9"/>
+      <c r="AA6" s="9"/>
+      <c r="AB6" s="9"/>
+      <c r="AC6" s="9"/>
+      <c r="AD6" s="9"/>
+      <c r="AE6" s="12"/>
     </row>
-    <row r="7" ht="15.75" customHeight="1">
-      <c r="A7" s="18"/>
-      <c r="B7" s="22" t="s">
+    <row r="7" spans="1:31" ht="15.75" customHeight="1">
+      <c r="A7" s="39"/>
+      <c r="B7" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="C7" s="23" t="s">
+      <c r="C7" s="17" t="s">
         <v>16</v>
       </c>
-      <c r="D7" s="21" t="s">
+      <c r="D7" s="15" t="s">
         <v>7</v>
       </c>
-      <c r="E7" s="14" t="s">
+      <c r="E7" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="F7" s="14" t="s">
+      <c r="F7" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="G7" s="14" t="s">
+      <c r="G7" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="H7" s="14" t="s">
+      <c r="H7" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="I7" s="14" t="s">
+      <c r="I7" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="J7" s="21" t="s">
+      <c r="J7" s="15" t="s">
         <v>10</v>
       </c>
-      <c r="K7" s="21" t="s">
+      <c r="K7" s="15" t="s">
         <v>7</v>
       </c>
-      <c r="L7" s="14" t="s">
+      <c r="L7" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="M7" s="14" t="s">
+      <c r="M7" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="N7" s="14" t="s">
+      <c r="N7" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="O7" s="14" t="s">
+      <c r="O7" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="P7" s="14" t="s">
+      <c r="P7" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="Q7" s="21" t="s">
+      <c r="Q7" s="15" t="s">
         <v>10</v>
       </c>
-      <c r="R7" s="21" t="s">
+      <c r="R7" s="15" t="s">
         <v>7</v>
       </c>
-      <c r="S7" s="14" t="s">
+      <c r="S7" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="T7" s="14"/>
-      <c r="U7" s="14"/>
-      <c r="V7" s="14"/>
-      <c r="W7" s="15"/>
-      <c r="X7" s="13"/>
-      <c r="Y7" s="13"/>
-      <c r="Z7" s="14"/>
-      <c r="AA7" s="14"/>
-      <c r="AB7" s="14"/>
-      <c r="AC7" s="14"/>
-      <c r="AD7" s="14"/>
-      <c r="AE7" s="17"/>
+      <c r="T7" s="9"/>
+      <c r="U7" s="9"/>
+      <c r="V7" s="9"/>
+      <c r="W7" s="10"/>
+      <c r="X7" s="8"/>
+      <c r="Y7" s="8"/>
+      <c r="Z7" s="9"/>
+      <c r="AA7" s="9"/>
+      <c r="AB7" s="9"/>
+      <c r="AC7" s="9"/>
+      <c r="AD7" s="9"/>
+      <c r="AE7" s="12"/>
     </row>
-    <row r="8" ht="15.75" customHeight="1">
-      <c r="A8" s="18"/>
-      <c r="B8" s="22" t="s">
+    <row r="8" spans="1:31" ht="15.75" customHeight="1">
+      <c r="A8" s="39"/>
+      <c r="B8" s="16" t="s">
         <v>17</v>
       </c>
-      <c r="C8" s="23" t="s">
+      <c r="C8" s="17" t="s">
         <v>18</v>
       </c>
-      <c r="D8" s="13"/>
-      <c r="E8" s="14"/>
-      <c r="F8" s="14"/>
-      <c r="G8" s="14"/>
-      <c r="H8" s="14"/>
-      <c r="I8" s="15"/>
-      <c r="J8" s="13"/>
-      <c r="K8" s="13"/>
-      <c r="L8" s="14"/>
-      <c r="M8" s="14"/>
-      <c r="N8" s="14"/>
-      <c r="O8" s="14"/>
-      <c r="P8" s="15"/>
-      <c r="Q8" s="13"/>
-      <c r="R8" s="13" t="s">
+      <c r="D8" s="8"/>
+      <c r="E8" s="9"/>
+      <c r="F8" s="9"/>
+      <c r="G8" s="9"/>
+      <c r="H8" s="9"/>
+      <c r="I8" s="10"/>
+      <c r="J8" s="8"/>
+      <c r="K8" s="8"/>
+      <c r="L8" s="9"/>
+      <c r="M8" s="9"/>
+      <c r="N8" s="9"/>
+      <c r="O8" s="9"/>
+      <c r="P8" s="10"/>
+      <c r="Q8" s="8"/>
+      <c r="R8" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="S8" s="14" t="s">
+      <c r="S8" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="T8" s="14"/>
-      <c r="U8" s="14"/>
-      <c r="V8" s="16"/>
-      <c r="W8" s="15"/>
-      <c r="X8" s="13"/>
-      <c r="Y8" s="13"/>
-      <c r="Z8" s="14"/>
-      <c r="AA8" s="14"/>
-      <c r="AB8" s="14"/>
-      <c r="AC8" s="14"/>
-      <c r="AD8" s="14"/>
-      <c r="AE8" s="17"/>
+      <c r="T8" s="9"/>
+      <c r="U8" s="9"/>
+      <c r="V8" s="11"/>
+      <c r="W8" s="10"/>
+      <c r="X8" s="8"/>
+      <c r="Y8" s="8"/>
+      <c r="Z8" s="9"/>
+      <c r="AA8" s="9"/>
+      <c r="AB8" s="9"/>
+      <c r="AC8" s="9"/>
+      <c r="AD8" s="9"/>
+      <c r="AE8" s="12"/>
     </row>
-    <row r="9" ht="15.75" customHeight="1">
-      <c r="A9" s="18"/>
-      <c r="B9" s="22" t="s">
+    <row r="9" spans="1:31" ht="15.75" customHeight="1">
+      <c r="A9" s="39"/>
+      <c r="B9" s="16" t="s">
         <v>19</v>
       </c>
-      <c r="C9" s="23" t="s">
+      <c r="C9" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="D9" s="13"/>
-      <c r="E9" s="14"/>
-      <c r="F9" s="14"/>
-      <c r="G9" s="14"/>
-      <c r="H9" s="14"/>
-      <c r="I9" s="15"/>
-      <c r="J9" s="13"/>
-      <c r="K9" s="13"/>
-      <c r="L9" s="14"/>
-      <c r="M9" s="14"/>
-      <c r="N9" s="14"/>
-      <c r="O9" s="14"/>
-      <c r="P9" s="15"/>
-      <c r="Q9" s="13"/>
-      <c r="R9" s="13"/>
-      <c r="S9" s="14"/>
-      <c r="T9" s="14"/>
-      <c r="U9" s="14"/>
-      <c r="V9" s="14"/>
-      <c r="W9" s="15"/>
-      <c r="X9" s="13"/>
-      <c r="Y9" s="13"/>
-      <c r="Z9" s="14"/>
-      <c r="AA9" s="14"/>
-      <c r="AB9" s="14"/>
-      <c r="AC9" s="14"/>
-      <c r="AD9" s="15"/>
-      <c r="AE9" s="17"/>
+      <c r="D9" s="8"/>
+      <c r="E9" s="9"/>
+      <c r="F9" s="9"/>
+      <c r="G9" s="9"/>
+      <c r="H9" s="9"/>
+      <c r="I9" s="10"/>
+      <c r="J9" s="8"/>
+      <c r="K9" s="8"/>
+      <c r="L9" s="9"/>
+      <c r="M9" s="9"/>
+      <c r="N9" s="9"/>
+      <c r="O9" s="9"/>
+      <c r="P9" s="10"/>
+      <c r="Q9" s="8"/>
+      <c r="R9" s="8"/>
+      <c r="S9" s="9"/>
+      <c r="T9" s="9"/>
+      <c r="U9" s="9"/>
+      <c r="V9" s="9"/>
+      <c r="W9" s="10"/>
+      <c r="X9" s="8"/>
+      <c r="Y9" s="8"/>
+      <c r="Z9" s="9"/>
+      <c r="AA9" s="9"/>
+      <c r="AB9" s="9"/>
+      <c r="AC9" s="9"/>
+      <c r="AD9" s="10"/>
+      <c r="AE9" s="12"/>
     </row>
-    <row r="10" ht="15.75" customHeight="1">
-      <c r="A10" s="18"/>
-      <c r="B10" s="22" t="s">
+    <row r="10" spans="1:31" ht="15.75" customHeight="1">
+      <c r="A10" s="39"/>
+      <c r="B10" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="C10" s="23" t="s">
+      <c r="C10" s="17" t="s">
         <v>22</v>
       </c>
-      <c r="D10" s="13"/>
-      <c r="E10" s="14"/>
-      <c r="F10" s="14"/>
-      <c r="G10" s="14"/>
-      <c r="H10" s="14"/>
-      <c r="I10" s="15"/>
-      <c r="J10" s="13"/>
-      <c r="K10" s="13"/>
-      <c r="L10" s="14"/>
-      <c r="M10" s="14"/>
-      <c r="N10" s="14"/>
-      <c r="O10" s="14"/>
-      <c r="P10" s="15"/>
-      <c r="Q10" s="13"/>
-      <c r="R10" s="13"/>
-      <c r="S10" s="14"/>
-      <c r="T10" s="14"/>
-      <c r="U10" s="14"/>
-      <c r="V10" s="14" t="s">
+      <c r="D10" s="8"/>
+      <c r="E10" s="9"/>
+      <c r="F10" s="9"/>
+      <c r="G10" s="9"/>
+      <c r="H10" s="9"/>
+      <c r="I10" s="10"/>
+      <c r="J10" s="8"/>
+      <c r="K10" s="8"/>
+      <c r="L10" s="9"/>
+      <c r="M10" s="9"/>
+      <c r="N10" s="9"/>
+      <c r="O10" s="9"/>
+      <c r="P10" s="10"/>
+      <c r="Q10" s="8"/>
+      <c r="R10" s="8"/>
+      <c r="S10" s="9"/>
+      <c r="T10" s="9"/>
+      <c r="U10" s="9"/>
+      <c r="V10" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="W10" s="14" t="s">
+      <c r="W10" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="X10" s="13" t="s">
+      <c r="X10" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="Y10" s="13" t="s">
+      <c r="Y10" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="Z10" s="14"/>
-      <c r="AA10" s="14"/>
-      <c r="AB10" s="14"/>
-      <c r="AC10" s="14"/>
-      <c r="AD10" s="14"/>
-      <c r="AE10" s="17"/>
+      <c r="Z10" s="9"/>
+      <c r="AA10" s="9"/>
+      <c r="AB10" s="9"/>
+      <c r="AC10" s="9"/>
+      <c r="AD10" s="9"/>
+      <c r="AE10" s="12"/>
     </row>
-    <row r="11" ht="15.75" customHeight="1">
-      <c r="A11" s="18"/>
-      <c r="B11" s="22" t="s">
+    <row r="11" spans="1:31" ht="15.75" customHeight="1">
+      <c r="A11" s="39"/>
+      <c r="B11" s="16" t="s">
         <v>23</v>
       </c>
-      <c r="C11" s="23" t="s">
+      <c r="C11" s="17" t="s">
         <v>24</v>
       </c>
-      <c r="D11" s="24"/>
-      <c r="E11" s="25"/>
-      <c r="F11" s="14"/>
-      <c r="G11" s="25"/>
-      <c r="H11" s="25"/>
-      <c r="I11" s="26"/>
-      <c r="J11" s="24"/>
-      <c r="K11" s="24"/>
-      <c r="L11" s="25"/>
-      <c r="M11" s="25"/>
-      <c r="N11" s="25"/>
-      <c r="O11" s="25"/>
-      <c r="P11" s="14"/>
-      <c r="Q11" s="24"/>
-      <c r="R11" s="24"/>
-      <c r="S11" s="25"/>
-      <c r="T11" s="25"/>
-      <c r="U11" s="25"/>
-      <c r="V11" s="14" t="s">
+      <c r="D11" s="18"/>
+      <c r="E11" s="19"/>
+      <c r="F11" s="9"/>
+      <c r="G11" s="19"/>
+      <c r="H11" s="19"/>
+      <c r="I11" s="20"/>
+      <c r="J11" s="18"/>
+      <c r="K11" s="18"/>
+      <c r="L11" s="19"/>
+      <c r="M11" s="19"/>
+      <c r="N11" s="19"/>
+      <c r="O11" s="19"/>
+      <c r="P11" s="9"/>
+      <c r="Q11" s="18"/>
+      <c r="R11" s="18"/>
+      <c r="S11" s="19"/>
+      <c r="T11" s="19"/>
+      <c r="U11" s="19"/>
+      <c r="V11" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="W11" s="14" t="s">
+      <c r="W11" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="X11" s="24" t="s">
+      <c r="X11" s="18" t="s">
         <v>6</v>
       </c>
-      <c r="Y11" s="24" t="s">
+      <c r="Y11" s="18" t="s">
         <v>6</v>
       </c>
-      <c r="Z11" s="25"/>
-      <c r="AA11" s="25"/>
-      <c r="AB11" s="25"/>
-      <c r="AC11" s="25"/>
-      <c r="AD11" s="25"/>
-      <c r="AE11" s="17"/>
+      <c r="Z11" s="19"/>
+      <c r="AA11" s="19"/>
+      <c r="AB11" s="19"/>
+      <c r="AC11" s="19"/>
+      <c r="AD11" s="19"/>
+      <c r="AE11" s="12"/>
     </row>
-    <row r="12" ht="15.75" customHeight="1">
-      <c r="A12" s="18"/>
-      <c r="B12" s="27" t="s">
+    <row r="12" spans="1:31" ht="15.75" customHeight="1">
+      <c r="A12" s="39"/>
+      <c r="B12" s="21" t="s">
         <v>25</v>
       </c>
-      <c r="C12" s="28" t="s">
+      <c r="C12" s="22" t="s">
         <v>26</v>
       </c>
-      <c r="D12" s="29"/>
-      <c r="E12" s="14"/>
-      <c r="F12" s="30"/>
-      <c r="G12" s="30"/>
-      <c r="H12" s="30"/>
-      <c r="I12" s="31" t="s">
+      <c r="D12" s="23"/>
+      <c r="E12" s="9"/>
+      <c r="F12" s="24"/>
+      <c r="G12" s="24"/>
+      <c r="H12" s="24"/>
+      <c r="I12" s="25" t="s">
         <v>6</v>
       </c>
-      <c r="J12" s="29" t="s">
+      <c r="J12" s="23" t="s">
         <v>7</v>
       </c>
-      <c r="K12" s="29" t="s">
+      <c r="K12" s="23" t="s">
         <v>7</v>
       </c>
-      <c r="L12" s="30"/>
-      <c r="M12" s="30"/>
-      <c r="N12" s="30"/>
-      <c r="O12" s="30"/>
-      <c r="P12" s="31"/>
-      <c r="Q12" s="29"/>
-      <c r="R12" s="29"/>
-      <c r="S12" s="30" t="s">
+      <c r="L12" s="24"/>
+      <c r="M12" s="24"/>
+      <c r="N12" s="24"/>
+      <c r="O12" s="24"/>
+      <c r="P12" s="25"/>
+      <c r="Q12" s="23"/>
+      <c r="R12" s="23"/>
+      <c r="S12" s="24" t="s">
         <v>7</v>
       </c>
-      <c r="T12" s="30"/>
-      <c r="U12" s="30"/>
-      <c r="V12" s="30"/>
-      <c r="W12" s="31"/>
-      <c r="X12" s="29"/>
-      <c r="Y12" s="13"/>
-      <c r="Z12" s="30"/>
-      <c r="AA12" s="30"/>
-      <c r="AB12" s="30"/>
-      <c r="AC12" s="30"/>
-      <c r="AD12" s="30"/>
-      <c r="AE12" s="17"/>
+      <c r="T12" s="24"/>
+      <c r="U12" s="24"/>
+      <c r="V12" s="24"/>
+      <c r="W12" s="25"/>
+      <c r="X12" s="23"/>
+      <c r="Y12" s="8"/>
+      <c r="Z12" s="24"/>
+      <c r="AA12" s="24"/>
+      <c r="AB12" s="24"/>
+      <c r="AC12" s="24"/>
+      <c r="AD12" s="24"/>
+      <c r="AE12" s="12"/>
     </row>
-    <row r="13" ht="15.75" customHeight="1">
-      <c r="A13" s="18"/>
-      <c r="B13" s="19" t="s">
+    <row r="13" spans="1:31" ht="15.75" customHeight="1">
+      <c r="A13" s="39"/>
+      <c r="B13" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="C13" s="20" t="s">
+      <c r="C13" s="14" t="s">
         <v>28</v>
       </c>
-      <c r="D13" s="21" t="s">
+      <c r="D13" s="15" t="s">
         <v>10</v>
       </c>
-      <c r="E13" s="21" t="s">
+      <c r="E13" s="15" t="s">
         <v>7</v>
       </c>
-      <c r="F13" s="14" t="s">
+      <c r="F13" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="G13" s="14" t="s">
+      <c r="G13" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="H13" s="14" t="s">
+      <c r="H13" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="I13" s="14" t="s">
+      <c r="I13" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="J13" s="21" t="s">
+      <c r="J13" s="15" t="s">
         <v>10</v>
       </c>
-      <c r="K13" s="21" t="s">
+      <c r="K13" s="15" t="s">
         <v>7</v>
       </c>
-      <c r="L13" s="14"/>
-      <c r="M13" s="14"/>
-      <c r="N13" s="14"/>
-      <c r="O13" s="14"/>
-      <c r="P13" s="14"/>
-      <c r="Q13" s="13"/>
-      <c r="R13" s="13"/>
-      <c r="S13" s="14"/>
-      <c r="T13" s="14"/>
-      <c r="U13" s="14"/>
-      <c r="V13" s="14"/>
-      <c r="W13" s="15"/>
-      <c r="X13" s="13"/>
-      <c r="Y13" s="13"/>
-      <c r="Z13" s="14"/>
-      <c r="AA13" s="14"/>
-      <c r="AB13" s="14"/>
-      <c r="AC13" s="14"/>
-      <c r="AD13" s="32" t="s">
+      <c r="L13" s="9"/>
+      <c r="M13" s="9"/>
+      <c r="N13" s="9"/>
+      <c r="O13" s="9"/>
+      <c r="P13" s="9"/>
+      <c r="Q13" s="8"/>
+      <c r="R13" s="8"/>
+      <c r="S13" s="9"/>
+      <c r="T13" s="9"/>
+      <c r="U13" s="9"/>
+      <c r="V13" s="9"/>
+      <c r="W13" s="10"/>
+      <c r="X13" s="8"/>
+      <c r="Y13" s="8"/>
+      <c r="Z13" s="9"/>
+      <c r="AA13" s="9"/>
+      <c r="AB13" s="9"/>
+      <c r="AC13" s="9"/>
+      <c r="AD13" s="26" t="s">
         <v>7</v>
       </c>
-      <c r="AE13" s="17"/>
+      <c r="AE13" s="12"/>
     </row>
-    <row r="14" ht="15.75" customHeight="1">
-      <c r="A14" s="18"/>
-      <c r="B14" s="19" t="s">
+    <row r="14" spans="1:31" ht="15.75" customHeight="1">
+      <c r="A14" s="39"/>
+      <c r="B14" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="C14" s="20" t="s">
+      <c r="C14" s="14" t="s">
         <v>31</v>
       </c>
-      <c r="D14" s="13"/>
-      <c r="E14" s="14"/>
-      <c r="F14" s="14"/>
-      <c r="G14" s="14"/>
-      <c r="H14" s="14"/>
-      <c r="I14" s="15"/>
-      <c r="J14" s="13"/>
-      <c r="K14" s="13" t="s">
+      <c r="D14" s="8"/>
+      <c r="E14" s="9"/>
+      <c r="F14" s="9"/>
+      <c r="G14" s="9"/>
+      <c r="H14" s="9"/>
+      <c r="I14" s="10"/>
+      <c r="J14" s="8"/>
+      <c r="K14" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="L14" s="14" t="s">
+      <c r="L14" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="M14" s="14"/>
-      <c r="N14" s="14"/>
-      <c r="O14" s="14"/>
-      <c r="P14" s="15"/>
-      <c r="Q14" s="13"/>
-      <c r="R14" s="33" t="s">
+      <c r="M14" s="9"/>
+      <c r="N14" s="9"/>
+      <c r="O14" s="9"/>
+      <c r="P14" s="10"/>
+      <c r="Q14" s="8"/>
+      <c r="R14" s="27" t="s">
         <v>7</v>
       </c>
-      <c r="S14" s="34" t="s">
+      <c r="S14" s="28" t="s">
         <v>10</v>
       </c>
-      <c r="T14" s="14"/>
-      <c r="U14" s="14"/>
-      <c r="V14" s="14"/>
-      <c r="W14" s="15"/>
-      <c r="X14" s="13"/>
-      <c r="Y14" s="13" t="s">
+      <c r="T14" s="9"/>
+      <c r="U14" s="9"/>
+      <c r="V14" s="9"/>
+      <c r="W14" s="10"/>
+      <c r="X14" s="8"/>
+      <c r="Y14" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="Z14" s="14" t="s">
+      <c r="Z14" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="AA14" s="14"/>
-      <c r="AB14" s="14"/>
-      <c r="AC14" s="14"/>
-      <c r="AD14" s="14"/>
-      <c r="AE14" s="17"/>
+      <c r="AA14" s="9"/>
+      <c r="AB14" s="9"/>
+      <c r="AC14" s="9"/>
+      <c r="AD14" s="9"/>
+      <c r="AE14" s="12"/>
     </row>
-    <row r="15" ht="15.75" customHeight="1">
-      <c r="A15" s="18"/>
-      <c r="B15" s="22" t="s">
+    <row r="15" spans="1:31" ht="15.75" customHeight="1">
+      <c r="A15" s="39"/>
+      <c r="B15" s="16" t="s">
         <v>32</v>
       </c>
-      <c r="C15" s="23" t="s">
+      <c r="C15" s="17" t="s">
         <v>33</v>
       </c>
-      <c r="D15" s="13"/>
-      <c r="E15" s="14"/>
-      <c r="F15" s="14"/>
-      <c r="G15" s="14"/>
-      <c r="H15" s="14"/>
-      <c r="I15" s="15"/>
-      <c r="J15" s="13"/>
-      <c r="K15" s="13"/>
-      <c r="L15" s="14"/>
-      <c r="M15" s="14"/>
-      <c r="N15" s="14"/>
-      <c r="O15" s="14"/>
-      <c r="P15" s="15"/>
-      <c r="Q15" s="13"/>
-      <c r="R15" s="13"/>
-      <c r="S15" s="14"/>
-      <c r="T15" s="14"/>
-      <c r="U15" s="14"/>
-      <c r="V15" s="14"/>
-      <c r="W15" s="15"/>
-      <c r="X15" s="13" t="s">
+      <c r="D15" s="8"/>
+      <c r="E15" s="9"/>
+      <c r="F15" s="9"/>
+      <c r="G15" s="9"/>
+      <c r="H15" s="9"/>
+      <c r="I15" s="10"/>
+      <c r="J15" s="8"/>
+      <c r="K15" s="8"/>
+      <c r="L15" s="9"/>
+      <c r="M15" s="9"/>
+      <c r="N15" s="9"/>
+      <c r="O15" s="9"/>
+      <c r="P15" s="10"/>
+      <c r="Q15" s="8"/>
+      <c r="R15" s="8"/>
+      <c r="S15" s="9"/>
+      <c r="T15" s="9"/>
+      <c r="U15" s="9"/>
+      <c r="V15" s="9"/>
+      <c r="W15" s="10"/>
+      <c r="X15" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="Y15" s="13" t="s">
+      <c r="Y15" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="Z15" s="14" t="s">
+      <c r="Z15" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="AA15" s="14"/>
-      <c r="AB15" s="14"/>
-      <c r="AC15" s="14"/>
-      <c r="AD15" s="14"/>
-      <c r="AE15" s="17"/>
+      <c r="AA15" s="9"/>
+      <c r="AB15" s="9"/>
+      <c r="AC15" s="9"/>
+      <c r="AD15" s="9"/>
+      <c r="AE15" s="12"/>
     </row>
-    <row r="16" ht="15.75" customHeight="1">
-      <c r="A16" s="18"/>
-      <c r="B16" s="19" t="s">
+    <row r="16" spans="1:31" ht="15.75" customHeight="1">
+      <c r="A16" s="39"/>
+      <c r="B16" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C16" s="20" t="s">
+      <c r="C16" s="14" t="s">
         <v>35</v>
       </c>
-      <c r="D16" s="13" t="s">
+      <c r="D16" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="E16" s="14" t="s">
+      <c r="E16" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="F16" s="14"/>
-      <c r="G16" s="14"/>
-      <c r="H16" s="14"/>
-      <c r="I16" s="13" t="s">
+      <c r="F16" s="9"/>
+      <c r="G16" s="9"/>
+      <c r="H16" s="9"/>
+      <c r="I16" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="J16" s="14" t="s">
+      <c r="J16" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="K16" s="15" t="s">
+      <c r="K16" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="L16" s="14"/>
-      <c r="M16" s="14"/>
-      <c r="N16" s="14"/>
-      <c r="O16" s="14"/>
-      <c r="P16" s="14"/>
-      <c r="Q16" s="13"/>
-      <c r="R16" s="13"/>
-      <c r="S16" s="14"/>
-      <c r="T16" s="14"/>
-      <c r="U16" s="14"/>
-      <c r="V16" s="14"/>
-      <c r="W16" s="15"/>
-      <c r="X16" s="13"/>
-      <c r="Y16" s="13"/>
-      <c r="Z16" s="14"/>
-      <c r="AA16" s="14"/>
-      <c r="AB16" s="14"/>
-      <c r="AC16" s="14"/>
-      <c r="AD16" s="32" t="s">
+      <c r="L16" s="9"/>
+      <c r="M16" s="9"/>
+      <c r="N16" s="9"/>
+      <c r="O16" s="9"/>
+      <c r="P16" s="9"/>
+      <c r="Q16" s="8"/>
+      <c r="R16" s="8"/>
+      <c r="S16" s="9"/>
+      <c r="T16" s="9"/>
+      <c r="U16" s="9"/>
+      <c r="V16" s="9"/>
+      <c r="W16" s="10"/>
+      <c r="X16" s="8"/>
+      <c r="Y16" s="8"/>
+      <c r="Z16" s="9"/>
+      <c r="AA16" s="9"/>
+      <c r="AB16" s="9"/>
+      <c r="AC16" s="9"/>
+      <c r="AD16" s="26" t="s">
         <v>7</v>
       </c>
-      <c r="AE16" s="17"/>
+      <c r="AE16" s="12"/>
     </row>
-    <row r="17" ht="15.75" customHeight="1">
-      <c r="A17" s="18"/>
-      <c r="B17" s="19" t="s">
+    <row r="17" spans="1:31" ht="15.75" customHeight="1">
+      <c r="A17" s="39"/>
+      <c r="B17" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="C17" s="20" t="s">
+      <c r="C17" s="14" t="s">
         <v>37</v>
       </c>
-      <c r="D17" s="13"/>
-      <c r="E17" s="14"/>
-      <c r="F17" s="14"/>
-      <c r="G17" s="14"/>
-      <c r="H17" s="14"/>
-      <c r="I17" s="15"/>
-      <c r="J17" s="13"/>
-      <c r="K17" s="14"/>
-      <c r="L17" s="14"/>
-      <c r="M17" s="14"/>
-      <c r="N17" s="14"/>
-      <c r="O17" s="14"/>
-      <c r="P17" s="15"/>
-      <c r="Q17" s="13"/>
-      <c r="R17" s="13"/>
-      <c r="S17" s="14"/>
-      <c r="T17" s="14" t="s">
+      <c r="D17" s="8"/>
+      <c r="E17" s="9"/>
+      <c r="F17" s="9"/>
+      <c r="G17" s="9"/>
+      <c r="H17" s="9"/>
+      <c r="I17" s="10"/>
+      <c r="J17" s="8"/>
+      <c r="K17" s="9"/>
+      <c r="L17" s="9"/>
+      <c r="M17" s="9"/>
+      <c r="N17" s="9"/>
+      <c r="O17" s="9"/>
+      <c r="P17" s="10"/>
+      <c r="Q17" s="8"/>
+      <c r="R17" s="8"/>
+      <c r="S17" s="9"/>
+      <c r="T17" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="U17" s="14"/>
-      <c r="V17" s="14"/>
-      <c r="W17" s="15"/>
-      <c r="X17" s="13"/>
-      <c r="Y17" s="13" t="s">
+      <c r="U17" s="9"/>
+      <c r="V17" s="9"/>
+      <c r="W17" s="10"/>
+      <c r="X17" s="8"/>
+      <c r="Y17" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="Z17" s="14" t="s">
+      <c r="Z17" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="AA17" s="14"/>
-      <c r="AB17" s="14"/>
-      <c r="AC17" s="14"/>
-      <c r="AD17" s="14"/>
-      <c r="AE17" s="17"/>
+      <c r="AA17" s="9"/>
+      <c r="AB17" s="9"/>
+      <c r="AC17" s="9"/>
+      <c r="AD17" s="9"/>
+      <c r="AE17" s="12"/>
     </row>
-    <row r="18" ht="15.75" customHeight="1">
-      <c r="A18" s="18"/>
-      <c r="B18" s="19" t="s">
+    <row r="18" spans="1:31" ht="15.75" customHeight="1">
+      <c r="A18" s="39"/>
+      <c r="B18" s="13" t="s">
         <v>39</v>
       </c>
-      <c r="C18" s="20" t="s">
+      <c r="C18" s="14" t="s">
         <v>40</v>
       </c>
-      <c r="D18" s="13"/>
-      <c r="E18" s="14"/>
-      <c r="F18" s="14" t="s">
+      <c r="D18" s="8"/>
+      <c r="E18" s="9"/>
+      <c r="F18" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="G18" s="14"/>
-      <c r="H18" s="14"/>
-      <c r="I18" s="15"/>
-      <c r="J18" s="13"/>
-      <c r="K18" s="13"/>
-      <c r="L18" s="14"/>
-      <c r="M18" s="14"/>
-      <c r="N18" s="14"/>
-      <c r="O18" s="14"/>
-      <c r="P18" s="15" t="s">
+      <c r="G18" s="9"/>
+      <c r="H18" s="9"/>
+      <c r="I18" s="10"/>
+      <c r="J18" s="8"/>
+      <c r="K18" s="8"/>
+      <c r="L18" s="9"/>
+      <c r="M18" s="9"/>
+      <c r="N18" s="9"/>
+      <c r="O18" s="9"/>
+      <c r="P18" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="Q18" s="13" t="s">
+      <c r="Q18" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="R18" s="13" t="s">
+      <c r="R18" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="S18" s="14"/>
-      <c r="T18" s="14"/>
-      <c r="U18" s="14"/>
-      <c r="V18" s="14"/>
-      <c r="W18" s="15"/>
-      <c r="X18" s="13"/>
-      <c r="Y18" s="13"/>
-      <c r="Z18" s="14"/>
-      <c r="AA18" s="14"/>
-      <c r="AB18" s="14"/>
-      <c r="AC18" s="14"/>
-      <c r="AD18" s="14"/>
-      <c r="AE18" s="17"/>
+      <c r="S18" s="9"/>
+      <c r="T18" s="9"/>
+      <c r="U18" s="9"/>
+      <c r="V18" s="9"/>
+      <c r="W18" s="10"/>
+      <c r="X18" s="8"/>
+      <c r="Y18" s="8"/>
+      <c r="Z18" s="9"/>
+      <c r="AA18" s="9"/>
+      <c r="AB18" s="9"/>
+      <c r="AC18" s="9"/>
+      <c r="AD18" s="9"/>
+      <c r="AE18" s="12"/>
     </row>
-    <row r="19" ht="15.75" customHeight="1">
-      <c r="A19" s="18"/>
-      <c r="B19" s="19" t="s">
+    <row r="19" spans="1:31" ht="15.75" customHeight="1">
+      <c r="A19" s="39"/>
+      <c r="B19" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="C19" s="20" t="s">
+      <c r="C19" s="14" t="s">
         <v>42</v>
       </c>
-      <c r="D19" s="14" t="s">
+      <c r="D19" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="E19" s="32" t="s">
+      <c r="E19" s="26" t="s">
         <v>43</v>
       </c>
-      <c r="F19" s="14" t="s">
+      <c r="F19" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="G19" s="14" t="s">
+      <c r="G19" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="H19" s="32" t="s">
+      <c r="H19" s="26" t="s">
         <v>29</v>
       </c>
-      <c r="I19" s="13" t="s">
+      <c r="I19" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="J19" s="13"/>
-      <c r="K19" s="13"/>
-      <c r="L19" s="14"/>
-      <c r="M19" s="14"/>
-      <c r="N19" s="14"/>
-      <c r="O19" s="14"/>
-      <c r="P19" s="15"/>
-      <c r="Q19" s="13"/>
-      <c r="R19" s="13"/>
-      <c r="S19" s="14"/>
-      <c r="T19" s="14"/>
-      <c r="U19" s="14"/>
-      <c r="V19" s="14"/>
-      <c r="W19" s="15"/>
-      <c r="X19" s="13"/>
-      <c r="Y19" s="13"/>
-      <c r="Z19" s="14"/>
-      <c r="AA19" s="14"/>
-      <c r="AB19" s="14"/>
-      <c r="AC19" s="14"/>
-      <c r="AD19" s="14"/>
-      <c r="AE19" s="32" t="s">
+      <c r="J19" s="8"/>
+      <c r="K19" s="8"/>
+      <c r="L19" s="9"/>
+      <c r="M19" s="9"/>
+      <c r="N19" s="9"/>
+      <c r="O19" s="9"/>
+      <c r="P19" s="10"/>
+      <c r="Q19" s="8"/>
+      <c r="R19" s="8"/>
+      <c r="S19" s="9"/>
+      <c r="T19" s="9"/>
+      <c r="U19" s="9"/>
+      <c r="V19" s="9"/>
+      <c r="W19" s="10"/>
+      <c r="X19" s="8"/>
+      <c r="Y19" s="8"/>
+      <c r="Z19" s="9"/>
+      <c r="AA19" s="9"/>
+      <c r="AB19" s="9"/>
+      <c r="AC19" s="9"/>
+      <c r="AD19" s="9"/>
+      <c r="AE19" s="26" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="20" ht="15.75" customHeight="1">
-      <c r="A20" s="18"/>
-      <c r="B20" s="35" t="s">
+    <row r="20" spans="1:31" ht="15.75" customHeight="1" thickBot="1">
+      <c r="A20" s="39"/>
+      <c r="B20" s="29" t="s">
         <v>44</v>
       </c>
-      <c r="C20" s="36" t="s">
+      <c r="C20" s="30" t="s">
         <v>45</v>
       </c>
-      <c r="D20" s="37"/>
-      <c r="E20" s="38"/>
-      <c r="F20" s="38"/>
-      <c r="G20" s="38"/>
-      <c r="H20" s="38"/>
-      <c r="I20" s="39"/>
-      <c r="J20" s="40"/>
-      <c r="K20" s="40" t="s">
+      <c r="D20" s="31"/>
+      <c r="E20" s="32"/>
+      <c r="F20" s="32"/>
+      <c r="G20" s="32"/>
+      <c r="H20" s="32"/>
+      <c r="I20" s="33"/>
+      <c r="J20" s="31"/>
+      <c r="K20" s="31"/>
+      <c r="L20" s="32"/>
+      <c r="M20" s="32"/>
+      <c r="N20" s="32" t="s">
         <v>7</v>
       </c>
-      <c r="L20" s="38"/>
-      <c r="M20" s="38"/>
-      <c r="N20" s="38"/>
-      <c r="O20" s="14"/>
-      <c r="P20" s="14"/>
-      <c r="Q20" s="40"/>
-      <c r="R20" s="40"/>
-      <c r="S20" s="38"/>
-      <c r="T20" s="38"/>
-      <c r="U20" s="38"/>
-      <c r="V20" s="38"/>
-      <c r="W20" s="39"/>
-      <c r="X20" s="40"/>
-      <c r="Y20" s="40" t="s">
+      <c r="O20" s="32"/>
+      <c r="P20" s="33"/>
+      <c r="Q20" s="31"/>
+      <c r="R20" s="31"/>
+      <c r="S20" s="32"/>
+      <c r="T20" s="32"/>
+      <c r="U20" s="32"/>
+      <c r="V20" s="32"/>
+      <c r="W20" s="33"/>
+      <c r="X20" s="31" t="s">
         <v>7</v>
       </c>
-      <c r="Z20" s="38"/>
-      <c r="AA20" s="38"/>
-      <c r="AB20" s="38"/>
-      <c r="AC20" s="38"/>
-      <c r="AD20" s="38"/>
-      <c r="AE20" s="17"/>
+      <c r="Y20" s="31" t="s">
+        <v>10</v>
+      </c>
+      <c r="Z20" s="32"/>
+      <c r="AA20" s="32"/>
+      <c r="AB20" s="32"/>
+      <c r="AC20" s="32"/>
+      <c r="AD20" s="32" t="s">
+        <v>10</v>
+      </c>
+      <c r="AE20" s="12"/>
     </row>
-    <row r="21" ht="15.75" customHeight="1">
-      <c r="A21" s="18"/>
-      <c r="B21" s="41" t="s">
+    <row r="21" spans="1:31" ht="15.75" customHeight="1" thickBot="1">
+      <c r="B21" s="40" t="s">
         <v>46</v>
       </c>
-      <c r="C21" s="42" t="s">
+      <c r="C21" s="41" t="s">
         <v>47</v>
       </c>
-      <c r="D21" s="43"/>
-      <c r="E21" s="44"/>
-      <c r="F21" s="44"/>
-      <c r="G21" s="44"/>
-      <c r="H21" s="44"/>
-      <c r="I21" s="45"/>
-      <c r="J21" s="43"/>
-      <c r="K21" s="43"/>
-      <c r="L21" s="44"/>
-      <c r="M21" s="44"/>
-      <c r="N21" s="44" t="s">
+      <c r="D21" s="48"/>
+      <c r="E21" s="49"/>
+      <c r="F21" s="49"/>
+      <c r="G21" s="49"/>
+      <c r="H21" s="49"/>
+      <c r="I21" s="49"/>
+      <c r="J21" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="O21" s="44"/>
-      <c r="P21" s="45"/>
-      <c r="Q21" s="43"/>
-      <c r="R21" s="43"/>
-      <c r="S21" s="44"/>
-      <c r="T21" s="44"/>
-      <c r="U21" s="44"/>
-      <c r="V21" s="44"/>
-      <c r="W21" s="45"/>
-      <c r="X21" s="43" t="s">
+      <c r="K21" s="48"/>
+      <c r="L21" s="49"/>
+      <c r="M21" s="49"/>
+      <c r="N21" s="49"/>
+      <c r="O21" s="49"/>
+      <c r="P21" s="51"/>
+      <c r="Q21" s="52" t="s">
+        <v>58</v>
+      </c>
+      <c r="R21" s="48"/>
+      <c r="S21" s="49"/>
+      <c r="T21" s="49"/>
+      <c r="U21" s="49" t="s">
+        <v>58</v>
+      </c>
+      <c r="V21" s="49"/>
+      <c r="W21" s="49"/>
+      <c r="X21" s="53"/>
+      <c r="Y21" s="48"/>
+      <c r="Z21" s="49"/>
+      <c r="AA21" s="49"/>
+      <c r="AB21" s="49"/>
+      <c r="AC21" s="49"/>
+      <c r="AD21" s="49" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="22" spans="1:31" ht="15.75" customHeight="1">
+      <c r="B22" s="42" t="s">
+        <v>48</v>
+      </c>
+      <c r="C22" s="43" t="s">
+        <v>49</v>
+      </c>
+      <c r="D22" s="54"/>
+      <c r="E22" s="55"/>
+      <c r="F22" s="55"/>
+      <c r="G22" s="55"/>
+      <c r="H22" s="55"/>
+      <c r="I22" s="55"/>
+      <c r="J22" s="56"/>
+      <c r="K22" s="54"/>
+      <c r="L22" s="55" t="s">
+        <v>58</v>
+      </c>
+      <c r="M22" s="55" t="s">
+        <v>59</v>
+      </c>
+      <c r="N22" s="55"/>
+      <c r="O22" s="55"/>
+      <c r="P22" s="57"/>
+      <c r="Q22" s="58"/>
+      <c r="R22" s="54"/>
+      <c r="S22" s="59"/>
+      <c r="T22" s="59"/>
+      <c r="U22" s="59"/>
+      <c r="V22" s="59"/>
+      <c r="W22" s="60"/>
+      <c r="X22" s="61" t="s">
+        <v>59</v>
+      </c>
+      <c r="Y22" s="54" t="s">
+        <v>58</v>
+      </c>
+      <c r="Z22" s="55"/>
+      <c r="AA22" s="55"/>
+      <c r="AB22" s="55"/>
+      <c r="AC22" s="55"/>
+      <c r="AD22" s="55"/>
+    </row>
+    <row r="23" spans="1:31" ht="15.75" customHeight="1" thickBot="1">
+      <c r="B23" s="40" t="s">
+        <v>50</v>
+      </c>
+      <c r="C23" s="41" t="s">
+        <v>51</v>
+      </c>
+      <c r="D23" s="48" t="s">
+        <v>58</v>
+      </c>
+      <c r="E23" s="49"/>
+      <c r="F23" s="49"/>
+      <c r="G23" s="49"/>
+      <c r="H23" s="49"/>
+      <c r="I23" s="49"/>
+      <c r="J23" s="50"/>
+      <c r="K23" s="48"/>
+      <c r="L23" s="49"/>
+      <c r="M23" s="49"/>
+      <c r="N23" s="49"/>
+      <c r="O23" s="49"/>
+      <c r="P23" s="51"/>
+      <c r="Q23" s="52" t="s">
+        <v>58</v>
+      </c>
+      <c r="R23" s="48"/>
+      <c r="S23" s="49"/>
+      <c r="T23" s="49"/>
+      <c r="U23" s="49" t="s">
+        <v>58</v>
+      </c>
+      <c r="V23" s="49"/>
+      <c r="W23" s="49"/>
+      <c r="X23" s="53"/>
+      <c r="Y23" s="48"/>
+      <c r="Z23" s="49"/>
+      <c r="AA23" s="49"/>
+      <c r="AB23" s="49" t="s">
+        <v>58</v>
+      </c>
+      <c r="AC23" s="49"/>
+      <c r="AD23" s="49"/>
+    </row>
+    <row r="24" spans="1:31" ht="15.75" customHeight="1">
+      <c r="B24" s="44" t="s">
+        <v>52</v>
+      </c>
+      <c r="C24" s="45" t="s">
+        <v>53</v>
+      </c>
+      <c r="D24" s="62"/>
+      <c r="E24" s="63"/>
+      <c r="F24" s="63"/>
+      <c r="G24" s="63"/>
+      <c r="H24" s="63"/>
+      <c r="I24" s="63" t="s">
+        <v>59</v>
+      </c>
+      <c r="J24" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="Y21" s="43" t="s">
-        <v>10</v>
-      </c>
-      <c r="Z21" s="44"/>
-      <c r="AA21" s="44"/>
-      <c r="AB21" s="44"/>
-      <c r="AC21" s="44"/>
-      <c r="AD21" s="44" t="s">
-        <v>10</v>
-      </c>
-      <c r="AE21" s="17"/>
+      <c r="K24" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="L24" s="63" t="s">
+        <v>59</v>
+      </c>
+      <c r="M24" s="63"/>
+      <c r="N24" s="63"/>
+      <c r="O24" s="63"/>
+      <c r="P24" s="64"/>
+      <c r="Q24" s="65"/>
+      <c r="R24" s="62"/>
+      <c r="S24" s="63"/>
+      <c r="T24" s="63"/>
+      <c r="U24" s="63"/>
+      <c r="V24" s="63"/>
+      <c r="W24" s="63"/>
+      <c r="X24" s="66"/>
+      <c r="Y24" s="62"/>
+      <c r="Z24" s="63"/>
+      <c r="AA24" s="63"/>
+      <c r="AB24" s="63"/>
+      <c r="AC24" s="63"/>
+      <c r="AD24" s="63"/>
     </row>
-    <row r="22" ht="15.75" customHeight="1"/>
-    <row r="23" ht="15.75" customHeight="1"/>
-    <row r="24" ht="15.75" customHeight="1"/>
-    <row r="25" ht="15.75" customHeight="1"/>
-    <row r="26" ht="15.75" customHeight="1"/>
-    <row r="27" ht="15.75" customHeight="1"/>
-    <row r="28" ht="15.75" customHeight="1"/>
-    <row r="29" ht="15.75" customHeight="1"/>
-    <row r="30" ht="15.75" customHeight="1"/>
-    <row r="31" ht="15.75" customHeight="1"/>
-    <row r="32" ht="15.75" customHeight="1"/>
+    <row r="25" spans="1:31" ht="15.75" customHeight="1">
+      <c r="B25" s="46" t="s">
+        <v>54</v>
+      </c>
+      <c r="C25" s="47" t="s">
+        <v>55</v>
+      </c>
+      <c r="D25" s="54"/>
+      <c r="E25" s="55"/>
+      <c r="F25" s="55"/>
+      <c r="G25" s="55"/>
+      <c r="H25" s="55"/>
+      <c r="I25" s="55"/>
+      <c r="J25" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="K25" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="L25" s="55" t="s">
+        <v>59</v>
+      </c>
+      <c r="M25" s="55"/>
+      <c r="N25" s="55"/>
+      <c r="O25" s="55"/>
+      <c r="P25" s="57"/>
+      <c r="Q25" s="58"/>
+      <c r="R25" s="54"/>
+      <c r="S25" s="55"/>
+      <c r="T25" s="55"/>
+      <c r="U25" s="55"/>
+      <c r="V25" s="55"/>
+      <c r="W25" s="55"/>
+      <c r="X25" s="61"/>
+      <c r="Y25" s="54"/>
+      <c r="Z25" s="55"/>
+      <c r="AA25" s="55"/>
+      <c r="AB25" s="55"/>
+      <c r="AC25" s="55"/>
+      <c r="AD25" s="55"/>
+    </row>
+    <row r="26" spans="1:31" ht="15.75" customHeight="1" thickBot="1">
+      <c r="B26" s="40" t="s">
+        <v>56</v>
+      </c>
+      <c r="C26" s="41" t="s">
+        <v>57</v>
+      </c>
+      <c r="D26" s="48"/>
+      <c r="E26" s="49"/>
+      <c r="F26" s="49"/>
+      <c r="G26" s="49"/>
+      <c r="H26" s="49"/>
+      <c r="I26" s="49"/>
+      <c r="J26" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="K26" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="L26" s="49"/>
+      <c r="M26" s="49"/>
+      <c r="N26" s="49"/>
+      <c r="O26" s="49"/>
+      <c r="P26" s="51"/>
+      <c r="Q26" s="52"/>
+      <c r="R26" s="48"/>
+      <c r="S26" s="67"/>
+      <c r="T26" s="67"/>
+      <c r="U26" s="67"/>
+      <c r="V26" s="67"/>
+      <c r="W26" s="68"/>
+      <c r="X26" s="53"/>
+      <c r="Y26" s="48"/>
+      <c r="Z26" s="49"/>
+      <c r="AA26" s="49"/>
+      <c r="AB26" s="49"/>
+      <c r="AC26" s="49"/>
+      <c r="AD26" s="49"/>
+    </row>
+    <row r="27" spans="1:31" ht="15.75" customHeight="1"/>
+    <row r="28" spans="1:31" ht="15.75" customHeight="1"/>
+    <row r="29" spans="1:31" ht="15.75" customHeight="1"/>
+    <row r="30" spans="1:31" ht="15.75" customHeight="1"/>
+    <row r="31" spans="1:31" ht="15.75" customHeight="1"/>
+    <row r="32" spans="1:31" ht="15.75" customHeight="1"/>
     <row r="33" ht="15.75" customHeight="1"/>
     <row r="34" ht="15.75" customHeight="1"/>
     <row r="35" ht="15.75" customHeight="1"/>
@@ -3032,16 +3727,74 @@
     <row r="997" ht="15.75" customHeight="1"/>
     <row r="998" ht="15.75" customHeight="1"/>
     <row r="999" ht="15.75" customHeight="1"/>
-    <row r="1000" ht="15.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
-    <mergeCell ref="A3:A21"/>
+    <mergeCell ref="A3:A20"/>
   </mergeCells>
-  <printOptions/>
-  <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>
+  <phoneticPr fontId="9" type="noConversion"/>
+  <conditionalFormatting sqref="E21:E26">
+    <cfRule type="containsText" dxfId="11" priority="10" operator="containsText" text="r">
+      <formula>NOT(ISERROR(SEARCH("r",E21)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D21:D26 F22:K23 F24:I26 F21:I21 K21">
+    <cfRule type="containsText" dxfId="10" priority="12" operator="containsText" text="r">
+      <formula>NOT(ISERROR(SEARCH("r",D21)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L21:O26">
+    <cfRule type="containsText" dxfId="9" priority="11" operator="containsText" text="r">
+      <formula>NOT(ISERROR(SEARCH("r",L21)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="Q21:AA21">
+    <cfRule type="containsText" dxfId="8" priority="9" operator="containsText" text="r">
+      <formula>NOT(ISERROR(SEARCH("r",Q21)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="P21">
+    <cfRule type="containsText" dxfId="7" priority="8" operator="containsText" text="r">
+      <formula>NOT(ISERROR(SEARCH("r",P21)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AB21:AD21">
+    <cfRule type="containsText" dxfId="6" priority="7" operator="containsText" text="r">
+      <formula>NOT(ISERROR(SEARCH("r",AB21)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="Q22:AA23">
+    <cfRule type="containsText" dxfId="5" priority="6" operator="containsText" text="r">
+      <formula>NOT(ISERROR(SEARCH("r",Q22)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="P22:P23">
+    <cfRule type="containsText" dxfId="4" priority="5" operator="containsText" text="r">
+      <formula>NOT(ISERROR(SEARCH("r",P22)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AB22:AD23">
+    <cfRule type="containsText" dxfId="3" priority="4" operator="containsText" text="r">
+      <formula>NOT(ISERROR(SEARCH("r",AB22)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="Q24:AA26">
+    <cfRule type="containsText" dxfId="2" priority="3" operator="containsText" text="r">
+      <formula>NOT(ISERROR(SEARCH("r",Q24)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="P24:P26">
+    <cfRule type="containsText" dxfId="1" priority="2" operator="containsText" text="r">
+      <formula>NOT(ISERROR(SEARCH("r",P24)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AB24:AD26">
+    <cfRule type="containsText" dxfId="0" priority="1" operator="containsText" text="r">
+      <formula>NOT(ISERROR(SEARCH("r",AB24)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="landscape"/>
-  <drawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/115年7月預劃匯入版 (1).xlsx
+++ b/115年7月預劃匯入版 (1).xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="204" uniqueCount="65">
   <si>
     <t>員編
 ID No.</t>
@@ -223,6 +223,24 @@
   <si>
     <t>r</t>
     <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>01夜B1</t>
+  </si>
+  <si>
+    <t>01夜B2</t>
+  </si>
+  <si>
+    <t>R</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>r</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>L</t>
+    <phoneticPr fontId="9" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -947,7 +965,7 @@
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="69">
+  <cellXfs count="71">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1050,6 +1068,99 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="30" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="31" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="32" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="33" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="34" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="35" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="36" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="37" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="30" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="38" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="39" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="38" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="31" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="39" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="36" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="40" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="41" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="40" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="37" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="40" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="40" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="41" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="34" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="42" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="42" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="35" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="43" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="38" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="38" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1067,93 +1178,6 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="0" borderId="30" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="0" borderId="31" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="0" borderId="32" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="0" borderId="33" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="0" borderId="34" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="0" borderId="35" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="0" borderId="36" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="0" borderId="37" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="30" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="38" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="39" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="38" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="31" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="39" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="36" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="40" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="41" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="40" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="37" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="40" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="40" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="41" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="34" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="42" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="42" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="35" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="43" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="38" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="38" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -1448,8 +1472,8 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:31" ht="30.75" customHeight="1">
-      <c r="A1" s="34"/>
-      <c r="B1" s="36" t="s">
+      <c r="A1" s="65"/>
+      <c r="B1" s="67" t="s">
         <v>0</v>
       </c>
       <c r="C1" s="1" t="s">
@@ -1541,8 +1565,8 @@
       </c>
     </row>
     <row r="2" spans="1:31" ht="15.75" customHeight="1">
-      <c r="A2" s="35"/>
-      <c r="B2" s="37"/>
+      <c r="A2" s="66"/>
+      <c r="B2" s="68"/>
       <c r="C2" s="3" t="s">
         <v>2</v>
       </c>
@@ -1656,8 +1680,8 @@
       </c>
       <c r="AE2" s="5"/>
     </row>
-    <row r="3" spans="1:31" ht="15.75" customHeight="1">
-      <c r="A3" s="38" t="s">
+    <row r="3" spans="1:31" ht="24.95" customHeight="1">
+      <c r="A3" s="69" t="s">
         <v>3</v>
       </c>
       <c r="B3" s="6" t="s">
@@ -1703,8 +1727,8 @@
       <c r="AD3" s="9"/>
       <c r="AE3" s="12"/>
     </row>
-    <row r="4" spans="1:31" ht="15.75" customHeight="1">
-      <c r="A4" s="39"/>
+    <row r="4" spans="1:31" ht="24.95" customHeight="1">
+      <c r="A4" s="70"/>
       <c r="B4" s="13" t="s">
         <v>8</v>
       </c>
@@ -1725,10 +1749,14 @@
       <c r="O4" s="9"/>
       <c r="P4" s="10"/>
       <c r="Q4" s="8"/>
-      <c r="R4" s="8"/>
+      <c r="R4" s="15" t="s">
+        <v>7</v>
+      </c>
       <c r="S4" s="9"/>
       <c r="T4" s="9"/>
-      <c r="U4" s="9"/>
+      <c r="U4" s="9" t="s">
+        <v>63</v>
+      </c>
       <c r="V4" s="9"/>
       <c r="W4" s="10"/>
       <c r="X4" s="8"/>
@@ -1748,8 +1776,8 @@
       <c r="AD4" s="9"/>
       <c r="AE4" s="12"/>
     </row>
-    <row r="5" spans="1:31" ht="15.75" customHeight="1">
-      <c r="A5" s="39"/>
+    <row r="5" spans="1:31" ht="24.95" customHeight="1">
+      <c r="A5" s="70"/>
       <c r="B5" s="13" t="s">
         <v>11</v>
       </c>
@@ -1793,8 +1821,8 @@
       <c r="AD5" s="9"/>
       <c r="AE5" s="12"/>
     </row>
-    <row r="6" spans="1:31" ht="15.75" customHeight="1">
-      <c r="A6" s="39"/>
+    <row r="6" spans="1:31" ht="24.95" customHeight="1">
+      <c r="A6" s="70"/>
       <c r="B6" s="13" t="s">
         <v>13</v>
       </c>
@@ -1840,8 +1868,8 @@
       <c r="AD6" s="9"/>
       <c r="AE6" s="12"/>
     </row>
-    <row r="7" spans="1:31" ht="15.75" customHeight="1">
-      <c r="A7" s="39"/>
+    <row r="7" spans="1:31" ht="24.95" customHeight="1">
+      <c r="A7" s="70"/>
       <c r="B7" s="16" t="s">
         <v>15</v>
       </c>
@@ -1909,8 +1937,8 @@
       <c r="AD7" s="9"/>
       <c r="AE7" s="12"/>
     </row>
-    <row r="8" spans="1:31" ht="15.75" customHeight="1">
-      <c r="A8" s="39"/>
+    <row r="8" spans="1:31" ht="24.95" customHeight="1">
+      <c r="A8" s="70"/>
       <c r="B8" s="16" t="s">
         <v>17</v>
       </c>
@@ -1950,45 +1978,101 @@
       <c r="AD8" s="9"/>
       <c r="AE8" s="12"/>
     </row>
-    <row r="9" spans="1:31" ht="15.75" customHeight="1">
-      <c r="A9" s="39"/>
+    <row r="9" spans="1:31" ht="24.95" customHeight="1">
+      <c r="A9" s="70"/>
       <c r="B9" s="16" t="s">
         <v>19</v>
       </c>
       <c r="C9" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="D9" s="8"/>
-      <c r="E9" s="9"/>
-      <c r="F9" s="9"/>
-      <c r="G9" s="9"/>
-      <c r="H9" s="9"/>
-      <c r="I9" s="10"/>
-      <c r="J9" s="8"/>
-      <c r="K9" s="8"/>
-      <c r="L9" s="9"/>
-      <c r="M9" s="9"/>
-      <c r="N9" s="9"/>
-      <c r="O9" s="9"/>
-      <c r="P9" s="10"/>
-      <c r="Q9" s="8"/>
-      <c r="R9" s="8"/>
-      <c r="S9" s="9"/>
-      <c r="T9" s="9"/>
-      <c r="U9" s="9"/>
-      <c r="V9" s="9"/>
-      <c r="W9" s="10"/>
-      <c r="X9" s="8"/>
-      <c r="Y9" s="8"/>
-      <c r="Z9" s="9"/>
-      <c r="AA9" s="9"/>
-      <c r="AB9" s="9"/>
-      <c r="AC9" s="9"/>
-      <c r="AD9" s="10"/>
-      <c r="AE9" s="12"/>
+      <c r="D9" s="15" t="s">
+        <v>60</v>
+      </c>
+      <c r="E9" s="63" t="s">
+        <v>61</v>
+      </c>
+      <c r="F9" s="63" t="s">
+        <v>60</v>
+      </c>
+      <c r="G9" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="H9" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="I9" s="10" t="s">
+        <v>64</v>
+      </c>
+      <c r="J9" s="15" t="s">
+        <v>60</v>
+      </c>
+      <c r="K9" s="15" t="s">
+        <v>61</v>
+      </c>
+      <c r="L9" s="63" t="s">
+        <v>60</v>
+      </c>
+      <c r="M9" s="63" t="s">
+        <v>61</v>
+      </c>
+      <c r="N9" s="63" t="s">
+        <v>60</v>
+      </c>
+      <c r="O9" s="26" t="s">
+        <v>62</v>
+      </c>
+      <c r="P9" s="26" t="s">
+        <v>6</v>
+      </c>
+      <c r="Q9" s="26" t="s">
+        <v>63</v>
+      </c>
+      <c r="R9" s="26" t="s">
+        <v>62</v>
+      </c>
+      <c r="S9" s="15" t="s">
+        <v>60</v>
+      </c>
+      <c r="T9" s="15" t="s">
+        <v>61</v>
+      </c>
+      <c r="U9" s="63" t="s">
+        <v>60</v>
+      </c>
+      <c r="V9" s="63" t="s">
+        <v>61</v>
+      </c>
+      <c r="W9" s="63" t="s">
+        <v>60</v>
+      </c>
+      <c r="X9" s="64" t="s">
+        <v>61</v>
+      </c>
+      <c r="Y9" s="26" t="s">
+        <v>62</v>
+      </c>
+      <c r="Z9" s="26" t="s">
+        <v>63</v>
+      </c>
+      <c r="AA9" s="10" t="s">
+        <v>63</v>
+      </c>
+      <c r="AB9" s="63" t="s">
+        <v>60</v>
+      </c>
+      <c r="AC9" s="63" t="s">
+        <v>61</v>
+      </c>
+      <c r="AD9" s="63" t="s">
+        <v>60</v>
+      </c>
+      <c r="AE9" s="63" t="s">
+        <v>61</v>
+      </c>
     </row>
-    <row r="10" spans="1:31" ht="15.75" customHeight="1">
-      <c r="A10" s="39"/>
+    <row r="10" spans="1:31" ht="24.95" customHeight="1">
+      <c r="A10" s="70"/>
       <c r="B10" s="16" t="s">
         <v>21</v>
       </c>
@@ -2006,10 +2090,18 @@
       <c r="L10" s="9"/>
       <c r="M10" s="9"/>
       <c r="N10" s="9"/>
-      <c r="O10" s="9"/>
-      <c r="P10" s="10"/>
-      <c r="Q10" s="8"/>
-      <c r="R10" s="8"/>
+      <c r="O10" s="15" t="s">
+        <v>60</v>
+      </c>
+      <c r="P10" s="15" t="s">
+        <v>61</v>
+      </c>
+      <c r="Q10" s="63" t="s">
+        <v>60</v>
+      </c>
+      <c r="R10" s="63" t="s">
+        <v>61</v>
+      </c>
       <c r="S10" s="9"/>
       <c r="T10" s="9"/>
       <c r="U10" s="9"/>
@@ -2030,10 +2122,12 @@
       <c r="AB10" s="9"/>
       <c r="AC10" s="9"/>
       <c r="AD10" s="9"/>
-      <c r="AE10" s="12"/>
+      <c r="AE10" s="12" t="s">
+        <v>62</v>
+      </c>
     </row>
-    <row r="11" spans="1:31" ht="15.75" customHeight="1">
-      <c r="A11" s="39"/>
+    <row r="11" spans="1:31" ht="24.95" customHeight="1" thickBot="1">
+      <c r="A11" s="70"/>
       <c r="B11" s="16" t="s">
         <v>23</v>
       </c>
@@ -2052,10 +2146,18 @@
       <c r="M11" s="19"/>
       <c r="N11" s="19"/>
       <c r="O11" s="19"/>
-      <c r="P11" s="9"/>
-      <c r="Q11" s="18"/>
-      <c r="R11" s="18"/>
-      <c r="S11" s="19"/>
+      <c r="P11" s="15" t="s">
+        <v>60</v>
+      </c>
+      <c r="Q11" s="15" t="s">
+        <v>61</v>
+      </c>
+      <c r="R11" s="63" t="s">
+        <v>60</v>
+      </c>
+      <c r="S11" s="63" t="s">
+        <v>61</v>
+      </c>
       <c r="T11" s="19"/>
       <c r="U11" s="19"/>
       <c r="V11" s="9" t="s">
@@ -2075,10 +2177,12 @@
       <c r="AB11" s="19"/>
       <c r="AC11" s="19"/>
       <c r="AD11" s="19"/>
-      <c r="AE11" s="12"/>
+      <c r="AE11" s="12" t="s">
+        <v>62</v>
+      </c>
     </row>
-    <row r="12" spans="1:31" ht="15.75" customHeight="1">
-      <c r="A12" s="39"/>
+    <row r="12" spans="1:31" ht="24.95" customHeight="1" thickTop="1">
+      <c r="A12" s="70"/>
       <c r="B12" s="21" t="s">
         <v>25</v>
       </c>
@@ -2122,8 +2226,8 @@
       <c r="AD12" s="24"/>
       <c r="AE12" s="12"/>
     </row>
-    <row r="13" spans="1:31" ht="15.75" customHeight="1">
-      <c r="A13" s="39"/>
+    <row r="13" spans="1:31" ht="24.95" customHeight="1">
+      <c r="A13" s="70"/>
       <c r="B13" s="13" t="s">
         <v>27</v>
       </c>
@@ -2177,16 +2281,20 @@
       </c>
       <c r="AE13" s="12"/>
     </row>
-    <row r="14" spans="1:31" ht="15.75" customHeight="1">
-      <c r="A14" s="39"/>
+    <row r="14" spans="1:31" ht="24.95" customHeight="1">
+      <c r="A14" s="70"/>
       <c r="B14" s="13" t="s">
         <v>30</v>
       </c>
       <c r="C14" s="14" t="s">
         <v>31</v>
       </c>
-      <c r="D14" s="8"/>
-      <c r="E14" s="9"/>
+      <c r="D14" s="27" t="s">
+        <v>7</v>
+      </c>
+      <c r="E14" s="28" t="s">
+        <v>10</v>
+      </c>
       <c r="F14" s="9"/>
       <c r="G14" s="9"/>
       <c r="H14" s="9"/>
@@ -2226,8 +2334,8 @@
       <c r="AD14" s="9"/>
       <c r="AE14" s="12"/>
     </row>
-    <row r="15" spans="1:31" ht="15.75" customHeight="1">
-      <c r="A15" s="39"/>
+    <row r="15" spans="1:31" ht="24.95" customHeight="1">
+      <c r="A15" s="70"/>
       <c r="B15" s="16" t="s">
         <v>32</v>
       </c>
@@ -2269,8 +2377,8 @@
       <c r="AD15" s="9"/>
       <c r="AE15" s="12"/>
     </row>
-    <row r="16" spans="1:31" ht="15.75" customHeight="1">
-      <c r="A16" s="39"/>
+    <row r="16" spans="1:31" ht="24.95" customHeight="1">
+      <c r="A16" s="70"/>
       <c r="B16" s="13" t="s">
         <v>34</v>
       </c>
@@ -2318,8 +2426,8 @@
       </c>
       <c r="AE16" s="12"/>
     </row>
-    <row r="17" spans="1:31" ht="15.75" customHeight="1">
-      <c r="A17" s="39"/>
+    <row r="17" spans="1:31" ht="24.95" customHeight="1">
+      <c r="A17" s="70"/>
       <c r="B17" s="13" t="s">
         <v>36</v>
       </c>
@@ -2361,8 +2469,8 @@
       <c r="AD17" s="9"/>
       <c r="AE17" s="12"/>
     </row>
-    <row r="18" spans="1:31" ht="15.75" customHeight="1">
-      <c r="A18" s="39"/>
+    <row r="18" spans="1:31" ht="24.95" customHeight="1">
+      <c r="A18" s="70"/>
       <c r="B18" s="13" t="s">
         <v>39</v>
       </c>
@@ -2406,8 +2514,8 @@
       <c r="AD18" s="9"/>
       <c r="AE18" s="12"/>
     </row>
-    <row r="19" spans="1:31" ht="15.75" customHeight="1">
-      <c r="A19" s="39"/>
+    <row r="19" spans="1:31" ht="24.95" customHeight="1">
+      <c r="A19" s="70"/>
       <c r="B19" s="13" t="s">
         <v>41</v>
       </c>
@@ -2457,8 +2565,8 @@
         <v>7</v>
       </c>
     </row>
-    <row r="20" spans="1:31" ht="15.75" customHeight="1" thickBot="1">
-      <c r="A20" s="39"/>
+    <row r="20" spans="1:31" ht="24.95" customHeight="1" thickBot="1">
+      <c r="A20" s="70"/>
       <c r="B20" s="29" t="s">
         <v>44</v>
       </c>
@@ -2502,148 +2610,148 @@
       </c>
       <c r="AE20" s="12"/>
     </row>
-    <row r="21" spans="1:31" ht="15.75" customHeight="1" thickBot="1">
-      <c r="B21" s="40" t="s">
+    <row r="21" spans="1:31" ht="24.95" customHeight="1" thickBot="1">
+      <c r="B21" s="34" t="s">
         <v>46</v>
       </c>
-      <c r="C21" s="41" t="s">
+      <c r="C21" s="35" t="s">
         <v>47</v>
       </c>
-      <c r="D21" s="48"/>
-      <c r="E21" s="49"/>
-      <c r="F21" s="49"/>
-      <c r="G21" s="49"/>
-      <c r="H21" s="49"/>
-      <c r="I21" s="49"/>
+      <c r="D21" s="42"/>
+      <c r="E21" s="43"/>
+      <c r="F21" s="43"/>
+      <c r="G21" s="43"/>
+      <c r="H21" s="43"/>
+      <c r="I21" s="43"/>
       <c r="J21" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="K21" s="48"/>
-      <c r="L21" s="49"/>
-      <c r="M21" s="49"/>
-      <c r="N21" s="49"/>
-      <c r="O21" s="49"/>
-      <c r="P21" s="51"/>
-      <c r="Q21" s="52" t="s">
+      <c r="K21" s="42"/>
+      <c r="L21" s="43"/>
+      <c r="M21" s="43"/>
+      <c r="N21" s="43"/>
+      <c r="O21" s="43"/>
+      <c r="P21" s="45"/>
+      <c r="Q21" s="46" t="s">
         <v>58</v>
       </c>
-      <c r="R21" s="48"/>
-      <c r="S21" s="49"/>
-      <c r="T21" s="49"/>
-      <c r="U21" s="49" t="s">
+      <c r="R21" s="42"/>
+      <c r="S21" s="43"/>
+      <c r="T21" s="43"/>
+      <c r="U21" s="43" t="s">
         <v>58</v>
       </c>
-      <c r="V21" s="49"/>
-      <c r="W21" s="49"/>
-      <c r="X21" s="53"/>
-      <c r="Y21" s="48"/>
-      <c r="Z21" s="49"/>
-      <c r="AA21" s="49"/>
-      <c r="AB21" s="49"/>
-      <c r="AC21" s="49"/>
-      <c r="AD21" s="49" t="s">
+      <c r="V21" s="43"/>
+      <c r="W21" s="43"/>
+      <c r="X21" s="47"/>
+      <c r="Y21" s="42"/>
+      <c r="Z21" s="43"/>
+      <c r="AA21" s="43"/>
+      <c r="AB21" s="43"/>
+      <c r="AC21" s="43"/>
+      <c r="AD21" s="43" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="22" spans="1:31" ht="15.75" customHeight="1">
-      <c r="B22" s="42" t="s">
+    <row r="22" spans="1:31" ht="24.95" customHeight="1">
+      <c r="B22" s="36" t="s">
         <v>48</v>
       </c>
-      <c r="C22" s="43" t="s">
+      <c r="C22" s="37" t="s">
         <v>49</v>
       </c>
-      <c r="D22" s="54"/>
-      <c r="E22" s="55"/>
-      <c r="F22" s="55"/>
-      <c r="G22" s="55"/>
-      <c r="H22" s="55"/>
-      <c r="I22" s="55"/>
-      <c r="J22" s="56"/>
-      <c r="K22" s="54"/>
-      <c r="L22" s="55" t="s">
+      <c r="D22" s="48"/>
+      <c r="E22" s="49"/>
+      <c r="F22" s="49"/>
+      <c r="G22" s="49"/>
+      <c r="H22" s="49"/>
+      <c r="I22" s="49"/>
+      <c r="J22" s="50"/>
+      <c r="K22" s="48"/>
+      <c r="L22" s="49" t="s">
         <v>58</v>
       </c>
-      <c r="M22" s="55" t="s">
+      <c r="M22" s="49" t="s">
         <v>59</v>
       </c>
-      <c r="N22" s="55"/>
-      <c r="O22" s="55"/>
-      <c r="P22" s="57"/>
-      <c r="Q22" s="58"/>
-      <c r="R22" s="54"/>
-      <c r="S22" s="59"/>
-      <c r="T22" s="59"/>
-      <c r="U22" s="59"/>
-      <c r="V22" s="59"/>
-      <c r="W22" s="60"/>
-      <c r="X22" s="61" t="s">
+      <c r="N22" s="49"/>
+      <c r="O22" s="49"/>
+      <c r="P22" s="51"/>
+      <c r="Q22" s="52"/>
+      <c r="R22" s="48"/>
+      <c r="S22" s="53"/>
+      <c r="T22" s="53"/>
+      <c r="U22" s="53"/>
+      <c r="V22" s="53"/>
+      <c r="W22" s="54"/>
+      <c r="X22" s="55" t="s">
         <v>59</v>
       </c>
-      <c r="Y22" s="54" t="s">
+      <c r="Y22" s="48" t="s">
         <v>58</v>
       </c>
-      <c r="Z22" s="55"/>
-      <c r="AA22" s="55"/>
-      <c r="AB22" s="55"/>
-      <c r="AC22" s="55"/>
-      <c r="AD22" s="55"/>
+      <c r="Z22" s="49"/>
+      <c r="AA22" s="49"/>
+      <c r="AB22" s="49"/>
+      <c r="AC22" s="49"/>
+      <c r="AD22" s="49"/>
     </row>
-    <row r="23" spans="1:31" ht="15.75" customHeight="1" thickBot="1">
-      <c r="B23" s="40" t="s">
+    <row r="23" spans="1:31" ht="24.95" customHeight="1" thickBot="1">
+      <c r="B23" s="34" t="s">
         <v>50</v>
       </c>
-      <c r="C23" s="41" t="s">
+      <c r="C23" s="35" t="s">
         <v>51</v>
       </c>
-      <c r="D23" s="48" t="s">
+      <c r="D23" s="42" t="s">
         <v>58</v>
       </c>
-      <c r="E23" s="49"/>
-      <c r="F23" s="49"/>
-      <c r="G23" s="49"/>
-      <c r="H23" s="49"/>
-      <c r="I23" s="49"/>
-      <c r="J23" s="50"/>
-      <c r="K23" s="48"/>
-      <c r="L23" s="49"/>
-      <c r="M23" s="49"/>
-      <c r="N23" s="49"/>
-      <c r="O23" s="49"/>
-      <c r="P23" s="51"/>
-      <c r="Q23" s="52" t="s">
+      <c r="E23" s="43"/>
+      <c r="F23" s="43"/>
+      <c r="G23" s="43"/>
+      <c r="H23" s="43"/>
+      <c r="I23" s="43"/>
+      <c r="J23" s="44"/>
+      <c r="K23" s="42"/>
+      <c r="L23" s="43"/>
+      <c r="M23" s="43"/>
+      <c r="N23" s="43"/>
+      <c r="O23" s="43"/>
+      <c r="P23" s="45"/>
+      <c r="Q23" s="46" t="s">
         <v>58</v>
       </c>
-      <c r="R23" s="48"/>
-      <c r="S23" s="49"/>
-      <c r="T23" s="49"/>
-      <c r="U23" s="49" t="s">
+      <c r="R23" s="42"/>
+      <c r="S23" s="43"/>
+      <c r="T23" s="43"/>
+      <c r="U23" s="43" t="s">
         <v>58</v>
       </c>
-      <c r="V23" s="49"/>
-      <c r="W23" s="49"/>
-      <c r="X23" s="53"/>
-      <c r="Y23" s="48"/>
-      <c r="Z23" s="49"/>
-      <c r="AA23" s="49"/>
-      <c r="AB23" s="49" t="s">
+      <c r="V23" s="43"/>
+      <c r="W23" s="43"/>
+      <c r="X23" s="47"/>
+      <c r="Y23" s="42"/>
+      <c r="Z23" s="43"/>
+      <c r="AA23" s="43"/>
+      <c r="AB23" s="43" t="s">
         <v>58</v>
       </c>
-      <c r="AC23" s="49"/>
-      <c r="AD23" s="49"/>
+      <c r="AC23" s="43"/>
+      <c r="AD23" s="43"/>
     </row>
-    <row r="24" spans="1:31" ht="15.75" customHeight="1">
-      <c r="B24" s="44" t="s">
+    <row r="24" spans="1:31" ht="24.95" customHeight="1">
+      <c r="B24" s="38" t="s">
         <v>52</v>
       </c>
-      <c r="C24" s="45" t="s">
+      <c r="C24" s="39" t="s">
         <v>53</v>
       </c>
-      <c r="D24" s="62"/>
-      <c r="E24" s="63"/>
-      <c r="F24" s="63"/>
-      <c r="G24" s="63"/>
-      <c r="H24" s="63"/>
-      <c r="I24" s="63" t="s">
+      <c r="D24" s="56"/>
+      <c r="E24" s="57"/>
+      <c r="F24" s="57"/>
+      <c r="G24" s="57"/>
+      <c r="H24" s="57"/>
+      <c r="I24" s="57" t="s">
         <v>59</v>
       </c>
       <c r="J24" s="10" t="s">
@@ -2652,107 +2760,107 @@
       <c r="K24" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="L24" s="63" t="s">
+      <c r="L24" s="57" t="s">
         <v>59</v>
       </c>
-      <c r="M24" s="63"/>
-      <c r="N24" s="63"/>
-      <c r="O24" s="63"/>
-      <c r="P24" s="64"/>
-      <c r="Q24" s="65"/>
-      <c r="R24" s="62"/>
-      <c r="S24" s="63"/>
-      <c r="T24" s="63"/>
-      <c r="U24" s="63"/>
-      <c r="V24" s="63"/>
-      <c r="W24" s="63"/>
-      <c r="X24" s="66"/>
-      <c r="Y24" s="62"/>
-      <c r="Z24" s="63"/>
-      <c r="AA24" s="63"/>
-      <c r="AB24" s="63"/>
-      <c r="AC24" s="63"/>
-      <c r="AD24" s="63"/>
+      <c r="M24" s="57"/>
+      <c r="N24" s="57"/>
+      <c r="O24" s="57"/>
+      <c r="P24" s="58"/>
+      <c r="Q24" s="59"/>
+      <c r="R24" s="56"/>
+      <c r="S24" s="57"/>
+      <c r="T24" s="57"/>
+      <c r="U24" s="57"/>
+      <c r="V24" s="57"/>
+      <c r="W24" s="57"/>
+      <c r="X24" s="60"/>
+      <c r="Y24" s="56"/>
+      <c r="Z24" s="57"/>
+      <c r="AA24" s="57"/>
+      <c r="AB24" s="57"/>
+      <c r="AC24" s="57"/>
+      <c r="AD24" s="57"/>
     </row>
-    <row r="25" spans="1:31" ht="15.75" customHeight="1">
-      <c r="B25" s="46" t="s">
+    <row r="25" spans="1:31" ht="24.95" customHeight="1">
+      <c r="B25" s="40" t="s">
         <v>54</v>
       </c>
-      <c r="C25" s="47" t="s">
+      <c r="C25" s="41" t="s">
         <v>55</v>
       </c>
-      <c r="D25" s="54"/>
-      <c r="E25" s="55"/>
-      <c r="F25" s="55"/>
-      <c r="G25" s="55"/>
-      <c r="H25" s="55"/>
-      <c r="I25" s="55"/>
+      <c r="D25" s="48"/>
+      <c r="E25" s="49"/>
+      <c r="F25" s="49"/>
+      <c r="G25" s="49"/>
+      <c r="H25" s="49"/>
+      <c r="I25" s="49"/>
       <c r="J25" s="10" t="s">
         <v>7</v>
       </c>
       <c r="K25" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="L25" s="55" t="s">
+      <c r="L25" s="49" t="s">
         <v>59</v>
       </c>
-      <c r="M25" s="55"/>
-      <c r="N25" s="55"/>
-      <c r="O25" s="55"/>
-      <c r="P25" s="57"/>
-      <c r="Q25" s="58"/>
-      <c r="R25" s="54"/>
-      <c r="S25" s="55"/>
-      <c r="T25" s="55"/>
-      <c r="U25" s="55"/>
-      <c r="V25" s="55"/>
-      <c r="W25" s="55"/>
-      <c r="X25" s="61"/>
-      <c r="Y25" s="54"/>
-      <c r="Z25" s="55"/>
-      <c r="AA25" s="55"/>
-      <c r="AB25" s="55"/>
-      <c r="AC25" s="55"/>
-      <c r="AD25" s="55"/>
+      <c r="M25" s="49"/>
+      <c r="N25" s="49"/>
+      <c r="O25" s="49"/>
+      <c r="P25" s="51"/>
+      <c r="Q25" s="52"/>
+      <c r="R25" s="48"/>
+      <c r="S25" s="49"/>
+      <c r="T25" s="49"/>
+      <c r="U25" s="49"/>
+      <c r="V25" s="49"/>
+      <c r="W25" s="49"/>
+      <c r="X25" s="55"/>
+      <c r="Y25" s="48"/>
+      <c r="Z25" s="49"/>
+      <c r="AA25" s="49"/>
+      <c r="AB25" s="49"/>
+      <c r="AC25" s="49"/>
+      <c r="AD25" s="49"/>
     </row>
-    <row r="26" spans="1:31" ht="15.75" customHeight="1" thickBot="1">
-      <c r="B26" s="40" t="s">
+    <row r="26" spans="1:31" ht="24.95" customHeight="1" thickBot="1">
+      <c r="B26" s="34" t="s">
         <v>56</v>
       </c>
-      <c r="C26" s="41" t="s">
+      <c r="C26" s="35" t="s">
         <v>57</v>
       </c>
-      <c r="D26" s="48"/>
-      <c r="E26" s="49"/>
-      <c r="F26" s="49"/>
-      <c r="G26" s="49"/>
-      <c r="H26" s="49"/>
-      <c r="I26" s="49"/>
+      <c r="D26" s="42"/>
+      <c r="E26" s="43"/>
+      <c r="F26" s="43"/>
+      <c r="G26" s="43"/>
+      <c r="H26" s="43"/>
+      <c r="I26" s="43"/>
       <c r="J26" s="10" t="s">
         <v>7</v>
       </c>
       <c r="K26" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="L26" s="49"/>
-      <c r="M26" s="49"/>
-      <c r="N26" s="49"/>
-      <c r="O26" s="49"/>
-      <c r="P26" s="51"/>
-      <c r="Q26" s="52"/>
-      <c r="R26" s="48"/>
-      <c r="S26" s="67"/>
-      <c r="T26" s="67"/>
-      <c r="U26" s="67"/>
-      <c r="V26" s="67"/>
-      <c r="W26" s="68"/>
-      <c r="X26" s="53"/>
-      <c r="Y26" s="48"/>
-      <c r="Z26" s="49"/>
-      <c r="AA26" s="49"/>
-      <c r="AB26" s="49"/>
-      <c r="AC26" s="49"/>
-      <c r="AD26" s="49"/>
+      <c r="L26" s="43"/>
+      <c r="M26" s="43"/>
+      <c r="N26" s="43"/>
+      <c r="O26" s="43"/>
+      <c r="P26" s="45"/>
+      <c r="Q26" s="46"/>
+      <c r="R26" s="42"/>
+      <c r="S26" s="61"/>
+      <c r="T26" s="61"/>
+      <c r="U26" s="61"/>
+      <c r="V26" s="61"/>
+      <c r="W26" s="62"/>
+      <c r="X26" s="47"/>
+      <c r="Y26" s="42"/>
+      <c r="Z26" s="43"/>
+      <c r="AA26" s="43"/>
+      <c r="AB26" s="43"/>
+      <c r="AC26" s="43"/>
+      <c r="AD26" s="43"/>
     </row>
     <row r="27" spans="1:31" ht="15.75" customHeight="1"/>
     <row r="28" spans="1:31" ht="15.75" customHeight="1"/>
